--- a/SSM_dataset_metric_matrix.xlsx
+++ b/SSM_dataset_metric_matrix.xlsx
@@ -2651,6 +2651,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
         <is>
@@ -4916,7 +4917,7 @@
       <c r="N37" s="42" t="inlineStr"/>
       <c r="O37" s="40" t="inlineStr">
         <is>
-          <t>Ozbay 等 2008（原文公式未核对）</t>
+          <t>Ozbay 等 2008（已对照原文 Eq. 7 核实）</t>
         </is>
       </c>
     </row>
@@ -5049,6 +5050,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
         <is>
@@ -6345,7 +6347,7 @@
       </c>
       <c r="J29" s="40" t="inlineStr">
         <is>
-          <t>Ozbay 等 2008（原文公式未核对）</t>
+          <t>Ozbay 等 2008（已对照原文 Eq. 7 核实）</t>
         </is>
       </c>
     </row>
@@ -13629,8 +13631,8 @@
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="E2:L2"/>
     <mergeCell ref="M2:S2"/>

--- a/SSM_dataset_metric_matrix.xlsx
+++ b/SSM_dataset_metric_matrix.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标所需数据" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'按指标类型分类'!$A$5:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'按碰撞类型分类'!$A$5:$J$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'条件明细'!$A$2:$E$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'按指标类型分类'!$A$5:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'按碰撞类型分类'!$A$5:$J$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'条件明细'!$A$2:$E$169</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1373,101 +1373,6 @@
         <t>[缺数据] 带朝向外框：没有周围车的外框和横向信息</t>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
-      <text>
-        <t>[C6] 车型/质量：没有车型字段，要按外框尺寸估车型和质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="G21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="I21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="J21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="K21" authorId="0" shapeId="0">
-      <text>
-        <t>[C6] 车型/质量：只区分机动车与行人/自行车，不区分货车；[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="M21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="N21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="O21" authorId="0" shapeId="0">
-      <text>
-        <t>[C6] 车型/质量：只有车辆、行人、骑车人、标志四类，不区分货车，要按外框尺寸估质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="P21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="Q21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="R21" authorId="0" shapeId="0">
-      <text>
-        <t>[C6] 车型/质量：物体类别只有"车辆"，不区分轿车和货车，要按外框尺寸估质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
-      <text>
-        <t>[C6] 车型/质量：只分车辆、行人、骑车人，不区分货车；[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
-      <text>
-        <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
-    <comment ref="U21" authorId="0" shapeId="0">
-      <text>
-        <t>数据里没有周围物体的 3D 轨迹，需先用 CV（3D 检测/单目深度）从画面重建，误差大</t>
-      </text>
-    </comment>
-    <comment ref="V21" authorId="0" shapeId="0">
-      <text>
-        <t>数据里没有周围物体的 3D 轨迹，需先用 CV（3D 检测/单目深度）从画面重建，误差大</t>
-      </text>
-    </comment>
-    <comment ref="W21" authorId="0" shapeId="0">
-      <text>
-        <t>[C6] 车型/质量：前车车型未知，按小汽车估质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1808,7 +1713,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>数据够，但要自己设定参数或阈值（反应时间、最大减速度、TTC 阈值、车辆质量等），结果会随设定变化；要设什么见"需自设什么"一列</t>
+          <t>数据够，但要自己设定参数或阈值（反应时间、最大减速度、安全时距等），结果会随设定变化；要设什么见"需自设什么"一列</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1777,7 @@
       <c r="A12" s="33" t="n"/>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>1. ◐ 和"需自设什么"一列：反应时间、最大减速度、TTC 阈值、车辆质量等数值，所有数据集都不提供，需要自己设定、在论文里写明，最好再做敏感性分析。例如 NHTSA 那篇论文（arXiv 2306.14657）里，RSS 的反应时间设成 1.924 秒时，判为"不安全"的状态明显偏多。（RSS 后来已从本表删除。）</t>
+          <t>1. ◐ 和"需自设什么"一列：反应时间、最大减速度、安全时距等数值，所有数据集都不提供，需要自己设定、在论文里写明，最好再做敏感性分析。例如 NHTSA 那篇论文（arXiv 2306.14657）里，RSS 的反应时间设成 1.924 秒时，判为"不安全"的状态明显偏多。（RSS 后来已从本表删除。）</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1785,7 @@
       <c r="A13" s="33" t="n"/>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>2. delta-V 需要质量：数据集一般只给车型，按车型取典型质量。</t>
+          <t>2. 2026-10-15 删掉了 delta-V：按原文（Laureshyn et al. 2017）的算法，小汽车之间不刹车的版本就是接近速度的一半，排名和接近速度完全一样；考虑撞前刹车的扩展版在普通场景里全是 0（demo 里最小 TTC 4.556 s，两车撞上之前都能停下）。排名比较里没有新信息，所以删掉，也就不再需要车辆质量。</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="26" min="1" max="1"/>
@@ -1975,7 +1880,7 @@
     <row r="2" ht="42" customHeight="1" s="26">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>记号：后车 F（通常是自车）、前车 L；d = 间距（后车车头到前车车尾）；v = 速度；Δv = v_F − v_L 接近速度（大于 0 表示在靠近）；a = 加速度；Δa = a_F − a_L；τ、ρ = 反应时间；a_max = 最大刹车减速度（取正数）；W = 车宽；L = 车长；δ = 两车外框最短距离；Δt = 时间步长；μ = 路面摩擦系数；g = 重力加速度</t>
+          <t>记号：后车 F（通常是自车）、前车 L；d = 间距（后车车头到前车车尾）；v = 速度；Δv = v_F − v_L 接近速度（大于 0 表示在靠近）；a = 加速度；Δa = a_F − a_L；τ = 反应时间；a_max = 最大刹车减速度（取正数）；W = 车宽；L = 车长；δ = 两车外框最短距离；Δt = 时间步长</t>
         </is>
       </c>
     </row>
@@ -3663,42 +3568,42 @@
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t>delta-V</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>change in velocity during a (potential) collision</t>
+          <t>crash index (Ozbay et al. 2008)</t>
         </is>
       </c>
       <c r="D29" s="41" t="inlineStr">
         <is>
-          <t>ΔV_F = m_L ÷ (m_F + m_L) × |v_F − v_L|（v 为速度向量）</t>
+          <t>CI = [(v_F + a_F·MTTC)² − (v_L + a_L·MTTC)²] ÷ 2 × 1 ÷ MTTC</t>
         </is>
       </c>
       <c r="E29" s="40" t="inlineStr">
         <is>
-          <t>假设撞上后两车粘在一起，各自的速度一下子变多少；轻的一方变化大</t>
+          <t>到撞上那一刻两车速度平方差（碰撞能量）除以还剩的时间；常见引用写法，需核对原文</t>
         </is>
       </c>
       <c r="F29" s="40" t="inlineStr">
         <is>
-          <t>两车速度向量、质量</t>
+          <t>两车速度、加速度、MTTC</t>
         </is>
       </c>
       <c r="G29" s="40" t="inlineStr">
         <is>
-          <t>车辆质量（按车型或外框大小估）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m²/s³</t>
         </is>
       </c>
       <c r="I29" s="40" t="inlineStr">
         <is>
-          <t>越大越严重</t>
+          <t>越大越危险</t>
         </is>
       </c>
       <c r="J29" s="42" t="inlineStr">
@@ -3706,170 +3611,94 @@
           <t>●</t>
         </is>
       </c>
-      <c r="K29" s="42" t="inlineStr">
+      <c r="K29" s="42" t="inlineStr"/>
+      <c r="L29" s="42" t="inlineStr"/>
+      <c r="M29" s="42" t="inlineStr"/>
+      <c r="N29" s="42" t="inlineStr"/>
+      <c r="O29" s="40" t="inlineStr">
+        <is>
+          <t>Ozbay 等 2008（已对照原文 Eq. 7 核实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="26">
+      <c r="A30" s="47" t="inlineStr">
+        <is>
+          <t>模型预测类</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>MPrISM</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>model predictive instantaneous safety metric</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>所有物体的状态</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
+        </is>
+      </c>
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="I30" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J30" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="K30" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="L30" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="M30" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="N30" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L29" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="M29" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N29" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="O29" s="40" t="inlineStr">
-        <is>
-          <t>事故重建；Shelby 2011；Extended Delta-V 见 Laureshyn 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" s="26">
-      <c r="A30" s="46" t="inlineStr">
-        <is>
-          <t>严重度类</t>
-        </is>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>crash index (Ozbay et al. 2008)</t>
-        </is>
-      </c>
-      <c r="D30" s="41" t="inlineStr">
-        <is>
-          <t>CI = [(v_F + a_F·MTTC)² − (v_L + a_L·MTTC)²] ÷ 2 × 1 ÷ MTTC</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>到撞上那一刻两车速度平方差（碰撞能量）除以还剩的时间；常见引用写法，需核对原文</t>
-        </is>
-      </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>两车速度、加速度、MTTC</t>
-        </is>
-      </c>
-      <c r="G30" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="40" t="inlineStr">
-        <is>
-          <t>m²/s³</t>
-        </is>
-      </c>
-      <c r="I30" s="40" t="inlineStr">
-        <is>
-          <t>越大越危险</t>
-        </is>
-      </c>
-      <c r="J30" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="K30" s="42" t="inlineStr"/>
-      <c r="L30" s="42" t="inlineStr"/>
-      <c r="M30" s="42" t="inlineStr"/>
-      <c r="N30" s="42" t="inlineStr"/>
       <c r="O30" s="40" t="inlineStr">
         <is>
-          <t>Ozbay 等 2008（已对照原文 Eq. 7 核实）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" s="26">
-      <c r="A31" s="47" t="inlineStr">
-        <is>
-          <t>模型预测类</t>
-        </is>
-      </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>MPrISM</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>model predictive instantaneous safety metric</t>
-        </is>
-      </c>
-      <c r="D31" s="41" t="inlineStr">
-        <is>
-          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
-        </is>
-      </c>
-      <c r="E31" s="40" t="inlineStr">
-        <is>
-          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
-        </is>
-      </c>
-      <c r="F31" s="40" t="inlineStr">
-        <is>
-          <t>所有物体的状态</t>
-        </is>
-      </c>
-      <c r="G31" s="40" t="inlineStr">
-        <is>
-          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
-        </is>
-      </c>
-      <c r="H31" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I31" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J31" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="K31" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="L31" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="M31" s="42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="N31" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O31" s="40" t="inlineStr">
-        <is>
           <t>Weng 等 2020</t>
         </is>
       </c>
     </row>
+    <row r="31" s="26"/>
     <row r="32" s="26"/>
     <row r="33" s="26"/>
     <row r="34" s="26"/>
@@ -3878,7 +3707,7 @@
     <row r="37" s="26"/>
     <row r="38" s="26"/>
   </sheetData>
-  <autoFilter ref="A5:O31"/>
+  <autoFilter ref="A5:O30"/>
   <mergeCells count="2">
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A2:O2"/>
@@ -3893,7 +3722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="26" min="1" max="1"/>
@@ -3918,7 +3747,7 @@
     <row r="2" ht="42" customHeight="1" s="26">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>记号：后车 F（通常是自车）、前车 L；d = 间距（后车车头到前车车尾）；v = 速度；Δv = v_F − v_L 接近速度（大于 0 表示在靠近）；a = 加速度；Δa = a_F − a_L；τ、ρ = 反应时间；a_max = 最大刹车减速度（取正数）；W = 车宽；L = 车长；δ = 两车外框最短距离；Δt = 时间步长；μ = 路面摩擦系数；g = 重力加速度</t>
+          <t>记号：后车 F（通常是自车）、前车 L；d = 间距（后车车头到前车车尾）；v = 速度；Δv = v_F − v_L 接近速度（大于 0 表示在靠近）；a = 加速度；Δa = a_F − a_L；τ = 反应时间；a_max = 最大刹车减速度（取正数）；W = 车宽；L = 车长；δ = 两车外框最短距离；Δt = 时间步长</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4604,7 @@
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
-          <t>delta-V</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="D21" s="40" t="inlineStr">
@@ -4785,32 +4614,32 @@
       </c>
       <c r="E21" s="41" t="inlineStr">
         <is>
-          <t>ΔV_F = m_L ÷ (m_F + m_L) × |v_F − v_L|（v 为速度向量）</t>
+          <t>CI = [(v_F + a_F·MTTC)² − (v_L + a_L·MTTC)²] ÷ 2 × 1 ÷ MTTC</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>假设撞上后两车粘在一起，各自的速度一下子变多少；轻的一方变化大</t>
+          <t>到撞上那一刻两车速度平方差（碰撞能量）除以还剩的时间；常见引用写法，需核对原文</t>
         </is>
       </c>
       <c r="G21" s="40" t="inlineStr">
         <is>
-          <t>车辆质量（按车型或外框大小估）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m²/s³</t>
         </is>
       </c>
       <c r="I21" s="40" t="inlineStr">
         <is>
-          <t>越大越严重</t>
+          <t>越大越危险</t>
         </is>
       </c>
       <c r="J21" s="40" t="inlineStr">
         <is>
-          <t>事故重建；Shelby 2011；Extended Delta-V 见 Laureshyn 2017</t>
+          <t>Ozbay 等 2008（已对照原文 Eq. 7 核实）</t>
         </is>
       </c>
     </row>
@@ -4827,42 +4656,42 @@
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MPrISM</t>
         </is>
       </c>
       <c r="D22" s="40" t="inlineStr">
         <is>
-          <t>严重度类</t>
+          <t>模型预测类</t>
         </is>
       </c>
       <c r="E22" s="41" t="inlineStr">
         <is>
-          <t>CI = [(v_F + a_F·MTTC)² − (v_L + a_L·MTTC)²] ÷ 2 × 1 ÷ MTTC</t>
+          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>到撞上那一刻两车速度平方差（碰撞能量）除以还剩的时间；常见引用写法，需核对原文</t>
+          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
         </is>
       </c>
       <c r="G22" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
         </is>
       </c>
       <c r="H22" s="40" t="inlineStr">
         <is>
-          <t>m²/s³</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I22" s="40" t="inlineStr">
         <is>
-          <t>越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J22" s="40" t="inlineStr">
         <is>
-          <t>Ozbay 等 2008（已对照原文 Eq. 7 核实）</t>
+          <t>Weng 等 2020</t>
         </is>
       </c>
     </row>
@@ -4874,47 +4703,47 @@
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C23" s="39" t="inlineStr">
         <is>
-          <t>MPrISM</t>
+          <t>速度 v</t>
         </is>
       </c>
       <c r="D23" s="40" t="inlineStr">
         <is>
-          <t>模型预测类</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E23" s="41" t="inlineStr">
         <is>
-          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
+          <t>v = √(v_x² + v_y²)</t>
         </is>
       </c>
       <c r="F23" s="40" t="inlineStr">
         <is>
-          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
+          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
         </is>
       </c>
       <c r="G23" s="40" t="inlineStr">
         <is>
-          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越大越严重（严重度）</t>
         </is>
       </c>
       <c r="J23" s="40" t="inlineStr">
         <is>
-          <t>Weng 等 2020</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4760,7 @@
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
-          <t>速度 v</t>
+          <t>加加速度 jerk</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr">
@@ -4941,12 +4770,12 @@
       </c>
       <c r="E24" s="41" t="inlineStr">
         <is>
-          <t>v = √(v_x² + v_y²)</t>
+          <t>jerk = da ÷ dt</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
+          <t>加速度变化得有多突然，例如猛踩刹车</t>
         </is>
       </c>
       <c r="G24" s="40" t="inlineStr">
@@ -4956,12 +4785,12 @@
       </c>
       <c r="H24" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m/s³</t>
         </is>
       </c>
       <c r="I24" s="40" t="inlineStr">
         <is>
-          <t>越大越严重（严重度）</t>
+          <t>绝对值越大越危险</t>
         </is>
       </c>
       <c r="J24" s="40" t="inlineStr">
@@ -4983,94 +4812,94 @@
       </c>
       <c r="C25" s="39" t="inlineStr">
         <is>
-          <t>加加速度 jerk</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="D25" s="40" t="inlineStr">
         <is>
+          <t>距离类</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>PSD = 到冲突点的剩余距离 ÷ [v² ÷ (2·a_max)]</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>剩下的距离够不够停车；小于 1 表示刹不住</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>最大可接受减速度 a_max</t>
+        </is>
+      </c>
+      <c r="H25" s="40" t="inlineStr">
+        <is>
+          <t>无单位</t>
+        </is>
+      </c>
+      <c r="I25" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J25" s="40" t="inlineStr">
+        <is>
+          <t>Allen 等 1978</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>变道/侧刮</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>最近距离 δ</t>
+        </is>
+      </c>
+      <c r="D26" s="40" t="inlineStr">
+        <is>
           <t>原始运动学量</t>
         </is>
       </c>
-      <c r="E25" s="41" t="inlineStr">
-        <is>
-          <t>jerk = da ÷ dt</t>
-        </is>
-      </c>
-      <c r="F25" s="40" t="inlineStr">
-        <is>
-          <t>加速度变化得有多突然，例如猛踩刹车</t>
-        </is>
-      </c>
-      <c r="G25" s="40" t="inlineStr">
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>δ = 两车外框（矩形）之间的最短距离</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>不分方向，两车车身最近的地方隔多远</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="40" t="inlineStr">
-        <is>
-          <t>m/s³</t>
-        </is>
-      </c>
-      <c r="I25" s="40" t="inlineStr">
-        <is>
-          <t>绝对值越大越危险</t>
-        </is>
-      </c>
-      <c r="J25" s="40" t="inlineStr">
+      <c r="H26" s="40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I26" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J26" s="40" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" s="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>追尾/跟车</t>
-        </is>
-      </c>
-      <c r="B26" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>PSD</t>
-        </is>
-      </c>
-      <c r="D26" s="40" t="inlineStr">
-        <is>
-          <t>距离类</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="inlineStr">
-        <is>
-          <t>PSD = 到冲突点的剩余距离 ÷ [v² ÷ (2·a_max)]</t>
-        </is>
-      </c>
-      <c r="F26" s="40" t="inlineStr">
-        <is>
-          <t>剩下的距离够不够停车；小于 1 表示刹不住</t>
-        </is>
-      </c>
-      <c r="G26" s="40" t="inlineStr">
-        <is>
-          <t>最大可接受减速度 a_max</t>
-        </is>
-      </c>
-      <c r="H26" s="40" t="inlineStr">
-        <is>
-          <t>无单位</t>
-        </is>
-      </c>
-      <c r="I26" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J26" s="40" t="inlineStr">
-        <is>
-          <t>Allen 等 1978</t>
         </is>
       </c>
     </row>
@@ -5087,7 +4916,7 @@
       </c>
       <c r="C27" s="39" t="inlineStr">
         <is>
-          <t>最近距离 δ</t>
+          <t>横向间距</t>
         </is>
       </c>
       <c r="D27" s="40" t="inlineStr">
@@ -5097,12 +4926,12 @@
       </c>
       <c r="E27" s="41" t="inlineStr">
         <is>
-          <t>δ = 两车外框（矩形）之间的最短距离</t>
+          <t>横向间距 = |横向偏移| − (W_F + W_L) ÷ 2</t>
         </is>
       </c>
       <c r="F27" s="40" t="inlineStr">
         <is>
-          <t>不分方向，两车车身最近的地方隔多远</t>
+          <t>并排时两车侧面之间隔多远；负数表示横向已经重叠</t>
         </is>
       </c>
       <c r="G27" s="40" t="inlineStr">
@@ -5139,7 +4968,7 @@
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
-          <t>横向间距</t>
+          <t>接近速度 Δv</t>
         </is>
       </c>
       <c r="D28" s="40" t="inlineStr">
@@ -5149,12 +4978,12 @@
       </c>
       <c r="E28" s="41" t="inlineStr">
         <is>
-          <t>横向间距 = |横向偏移| − (W_F + W_L) ÷ 2</t>
+          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
         </is>
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>并排时两车侧面之间隔多远；负数表示横向已经重叠</t>
+          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
         </is>
       </c>
       <c r="G28" s="40" t="inlineStr">
@@ -5164,12 +4993,12 @@
       </c>
       <c r="H28" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="I28" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越大越危险</t>
         </is>
       </c>
       <c r="J28" s="40" t="inlineStr">
@@ -5191,7 +5020,7 @@
       </c>
       <c r="C29" s="39" t="inlineStr">
         <is>
-          <t>接近速度 Δv</t>
+          <t>横向加速度 a_lat</t>
         </is>
       </c>
       <c r="D29" s="40" t="inlineStr">
@@ -5201,12 +5030,12 @@
       </c>
       <c r="E29" s="41" t="inlineStr">
         <is>
-          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+          <t>a_lat = v × ω ≈ v² ÷ R（R 为转弯半径）</t>
         </is>
       </c>
       <c r="F29" s="40" t="inlineStr">
         <is>
-          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+          <t>转向有多急，例如急打方向、急变道</t>
         </is>
       </c>
       <c r="G29" s="40" t="inlineStr">
@@ -5216,12 +5045,12 @@
       </c>
       <c r="H29" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m/s²</t>
         </is>
       </c>
       <c r="I29" s="40" t="inlineStr">
         <is>
-          <t>越大越危险</t>
+          <t>绝对值越大越危险</t>
         </is>
       </c>
       <c r="J29" s="40" t="inlineStr">
@@ -5243,7 +5072,7 @@
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
-          <t>横向加速度 a_lat</t>
+          <t>横摆角速度 ω</t>
         </is>
       </c>
       <c r="D30" s="40" t="inlineStr">
@@ -5253,12 +5082,12 @@
       </c>
       <c r="E30" s="41" t="inlineStr">
         <is>
-          <t>a_lat = v × ω ≈ v² ÷ R（R 为转弯半径）</t>
+          <t>ω = dθ ÷ dt（θ 为车头朝向）</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>转向有多急，例如急打方向、急变道</t>
+          <t>车头转得有多快，反映突然打方向</t>
         </is>
       </c>
       <c r="G30" s="40" t="inlineStr">
@@ -5268,7 +5097,7 @@
       </c>
       <c r="H30" s="40" t="inlineStr">
         <is>
-          <t>m/s²</t>
+          <t>rad/s</t>
         </is>
       </c>
       <c r="I30" s="40" t="inlineStr">
@@ -5295,22 +5124,22 @@
       </c>
       <c r="C31" s="39" t="inlineStr">
         <is>
-          <t>横摆角速度 ω</t>
+          <t>2D-TTC</t>
         </is>
       </c>
       <c r="D31" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E31" s="41" t="inlineStr">
         <is>
-          <t>ω = dθ ÷ dt（θ 为车头朝向）</t>
+          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
         </is>
       </c>
       <c r="F31" s="40" t="inlineStr">
         <is>
-          <t>车头转得有多快，反映突然打方向</t>
+          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
         </is>
       </c>
       <c r="G31" s="40" t="inlineStr">
@@ -5320,17 +5149,17 @@
       </c>
       <c r="H31" s="40" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I31" s="40" t="inlineStr">
         <is>
-          <t>绝对值越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J31" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5176,7 @@
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
-          <t>2D-TTC</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="D32" s="40" t="inlineStr">
@@ -5357,12 +5186,12 @@
       </c>
       <c r="E32" s="41" t="inlineStr">
         <is>
-          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
+          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
+          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
         </is>
       </c>
       <c r="G32" s="40" t="inlineStr">
@@ -5382,7 +5211,7 @@
       </c>
       <c r="J32" s="40" t="inlineStr">
         <is>
-          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
+          <t>Venthuruthiyil &amp; Chunchu 2022</t>
         </is>
       </c>
     </row>
@@ -5399,27 +5228,27 @@
       </c>
       <c r="C33" s="39" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>MPrISM</t>
         </is>
       </c>
       <c r="D33" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>模型预测类</t>
         </is>
       </c>
       <c r="E33" s="41" t="inlineStr">
         <is>
-          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
+          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
         </is>
       </c>
       <c r="F33" s="40" t="inlineStr">
         <is>
-          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
+          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
         </is>
       </c>
       <c r="G33" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
         </is>
       </c>
       <c r="H33" s="40" t="inlineStr">
@@ -5434,7 +5263,7 @@
       </c>
       <c r="J33" s="40" t="inlineStr">
         <is>
-          <t>Venthuruthiyil &amp; Chunchu 2022</t>
+          <t>Weng 等 2020</t>
         </is>
       </c>
     </row>
@@ -5446,37 +5275,37 @@
       </c>
       <c r="B34" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
-          <t>MPrISM</t>
+          <t>间距 d</t>
         </is>
       </c>
       <c r="D34" s="40" t="inlineStr">
         <is>
-          <t>模型预测类</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E34" s="41" t="inlineStr">
         <is>
-          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
+          <t>d = 前车车尾纵向位置 − 后车车头纵向位置</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
+          <t>沿行驶方向两车之间还隔多远；最基础的接近程度指标</t>
         </is>
       </c>
       <c r="G34" s="40" t="inlineStr">
         <is>
-          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I34" s="40" t="inlineStr">
@@ -5486,7 +5315,7 @@
       </c>
       <c r="J34" s="40" t="inlineStr">
         <is>
-          <t>Weng 等 2020</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5332,7 @@
       </c>
       <c r="C35" s="39" t="inlineStr">
         <is>
-          <t>间距 d</t>
+          <t>速度 v</t>
         </is>
       </c>
       <c r="D35" s="40" t="inlineStr">
@@ -5513,12 +5342,12 @@
       </c>
       <c r="E35" s="41" t="inlineStr">
         <is>
-          <t>d = 前车车尾纵向位置 − 后车车头纵向位置</t>
+          <t>v = √(v_x² + v_y²)</t>
         </is>
       </c>
       <c r="F35" s="40" t="inlineStr">
         <is>
-          <t>沿行驶方向两车之间还隔多远；最基础的接近程度指标</t>
+          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
         </is>
       </c>
       <c r="G35" s="40" t="inlineStr">
@@ -5528,12 +5357,12 @@
       </c>
       <c r="H35" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="I35" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越大越严重（严重度）</t>
         </is>
       </c>
       <c r="J35" s="40" t="inlineStr">
@@ -5555,7 +5384,7 @@
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
-          <t>速度 v</t>
+          <t>加加速度 jerk</t>
         </is>
       </c>
       <c r="D36" s="40" t="inlineStr">
@@ -5565,12 +5394,12 @@
       </c>
       <c r="E36" s="41" t="inlineStr">
         <is>
-          <t>v = √(v_x² + v_y²)</t>
+          <t>jerk = da ÷ dt</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
+          <t>加速度变化得有多突然，例如猛踩刹车</t>
         </is>
       </c>
       <c r="G36" s="40" t="inlineStr">
@@ -5580,12 +5409,12 @@
       </c>
       <c r="H36" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m/s³</t>
         </is>
       </c>
       <c r="I36" s="40" t="inlineStr">
         <is>
-          <t>越大越严重（严重度）</t>
+          <t>绝对值越大越危险</t>
         </is>
       </c>
       <c r="J36" s="40" t="inlineStr">
@@ -5607,22 +5436,22 @@
       </c>
       <c r="C37" s="39" t="inlineStr">
         <is>
-          <t>加加速度 jerk</t>
+          <t>TTC</t>
         </is>
       </c>
       <c r="D37" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E37" s="41" t="inlineStr">
         <is>
-          <t>jerk = da ÷ dt</t>
+          <t>TTC = d ÷ Δv（Δv &gt; 0；否则记为 ∞）</t>
         </is>
       </c>
       <c r="F37" s="40" t="inlineStr">
         <is>
-          <t>加速度变化得有多突然，例如猛踩刹车</t>
+          <t>两车都保持现在的速度，还剩几秒撞上</t>
         </is>
       </c>
       <c r="G37" s="40" t="inlineStr">
@@ -5632,17 +5461,17 @@
       </c>
       <c r="H37" s="40" t="inlineStr">
         <is>
-          <t>m/s³</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I37" s="40" t="inlineStr">
         <is>
-          <t>绝对值越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J37" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hayward 1972</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5488,7 @@
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
-          <t>TTC</t>
+          <t>RTTC (ITTC)</t>
         </is>
       </c>
       <c r="D38" s="40" t="inlineStr">
@@ -5669,12 +5498,12 @@
       </c>
       <c r="E38" s="41" t="inlineStr">
         <is>
-          <t>TTC = d ÷ Δv（Δv &gt; 0；否则记为 ∞）</t>
+          <t>RTTC = Δv ÷ d = 1 ÷ TTC（不在靠近时为 0）</t>
         </is>
       </c>
       <c r="F38" s="40" t="inlineStr">
         <is>
-          <t>两车都保持现在的速度，还剩几秒撞上</t>
+          <t>TTC 的倒数；不会出现无穷大，排序和求平均方便</t>
         </is>
       </c>
       <c r="G38" s="40" t="inlineStr">
@@ -5684,17 +5513,17 @@
       </c>
       <c r="H38" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>1/s</t>
         </is>
       </c>
       <c r="I38" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越大越危险</t>
         </is>
       </c>
       <c r="J38" s="40" t="inlineStr">
         <is>
-          <t>Hayward 1972</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5540,7 @@
       </c>
       <c r="C39" s="39" t="inlineStr">
         <is>
-          <t>RTTC (ITTC)</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="D39" s="40" t="inlineStr">
@@ -5721,32 +5550,32 @@
       </c>
       <c r="E39" s="41" t="inlineStr">
         <is>
-          <t>RTTC = Δv ÷ d = 1 ÷ TTC（不在靠近时为 0）</t>
+          <t>PET = t_后到者进入冲突区 − t_先到者离开冲突区</t>
         </is>
       </c>
       <c r="F39" s="40" t="inlineStr">
         <is>
-          <t>TTC 的倒数；不会出现无穷大，排序和求平均方便</t>
+          <t>两个人实际先后经过同一块区域，相差几秒</t>
         </is>
       </c>
       <c r="G39" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>冲突区的定义</t>
         </is>
       </c>
       <c r="H39" s="40" t="inlineStr">
         <is>
-          <t>1/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I39" s="40" t="inlineStr">
         <is>
-          <t>越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J39" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Allen 等 1978</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5592,7 @@
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D40" s="40" t="inlineStr">
@@ -5773,12 +5602,12 @@
       </c>
       <c r="E40" s="41" t="inlineStr">
         <is>
-          <t>PET = t_后到者进入冲突区 − t_先到者离开冲突区</t>
+          <t>GT = t̂_后到者进入冲突区 − t̂_先到者离开冲突区（t̂ 按当前速度和方向预测）</t>
         </is>
       </c>
       <c r="F40" s="40" t="inlineStr">
         <is>
-          <t>两个人实际先后经过同一块区域，相差几秒</t>
+          <t>预测的 PET；冲突发生之前就能算</t>
         </is>
       </c>
       <c r="G40" s="40" t="inlineStr">
@@ -5815,146 +5644,146 @@
       </c>
       <c r="C41" s="39" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DRAC</t>
         </is>
       </c>
       <c r="D41" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>减速度类</t>
         </is>
       </c>
       <c r="E41" s="41" t="inlineStr">
         <is>
-          <t>GT = t̂_后到者进入冲突区 − t̂_先到者离开冲突区（t̂ 按当前速度和方向预测）</t>
+          <t>DRAC = Δv² ÷ (2·d)（不在靠近时为 0）</t>
         </is>
       </c>
       <c r="F41" s="40" t="inlineStr">
         <is>
-          <t>预测的 PET；冲突发生之前就能算</t>
+          <t>在间距用完之前把接近速度降到 0，后车至少要多大的减速度</t>
         </is>
       </c>
       <c r="G41" s="40" t="inlineStr">
         <is>
-          <t>冲突区的定义</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m/s²</t>
         </is>
       </c>
       <c r="I41" s="40" t="inlineStr">
         <is>
+          <t>越大越危险</t>
+        </is>
+      </c>
+      <c r="J41" s="40" t="inlineStr">
+        <is>
+          <t>Almqvist 等 1991</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" s="26">
+      <c r="A42" s="45" t="inlineStr">
+        <is>
+          <t>交叉/转弯</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>最近距离 δ</t>
+        </is>
+      </c>
+      <c r="D42" s="40" t="inlineStr">
+        <is>
+          <t>原始运动学量</t>
+        </is>
+      </c>
+      <c r="E42" s="41" t="inlineStr">
+        <is>
+          <t>δ = 两车外框（矩形）之间的最短距离</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>不分方向，两车车身最近的地方隔多远</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I42" s="40" t="inlineStr">
+        <is>
           <t>越小越危险</t>
         </is>
       </c>
-      <c r="J41" s="40" t="inlineStr">
-        <is>
-          <t>Allen 等 1978</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" s="26">
-      <c r="A42" s="44" t="inlineStr">
-        <is>
-          <t>变道/侧刮</t>
-        </is>
-      </c>
-      <c r="B42" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C42" s="39" t="inlineStr">
-        <is>
-          <t>DRAC</t>
-        </is>
-      </c>
-      <c r="D42" s="40" t="inlineStr">
-        <is>
-          <t>减速度类</t>
-        </is>
-      </c>
-      <c r="E42" s="41" t="inlineStr">
-        <is>
-          <t>DRAC = Δv² ÷ (2·d)（不在靠近时为 0）</t>
-        </is>
-      </c>
-      <c r="F42" s="40" t="inlineStr">
-        <is>
-          <t>在间距用完之前把接近速度降到 0，后车至少要多大的减速度</t>
-        </is>
-      </c>
-      <c r="G42" s="40" t="inlineStr">
+      <c r="J42" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="40" t="inlineStr">
-        <is>
-          <t>m/s²</t>
-        </is>
-      </c>
-      <c r="I42" s="40" t="inlineStr">
+    </row>
+    <row r="43" s="26">
+      <c r="A43" s="45" t="inlineStr">
+        <is>
+          <t>交叉/转弯</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="inlineStr">
+        <is>
+          <t>接近速度 Δv</t>
+        </is>
+      </c>
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>原始运动学量</t>
+        </is>
+      </c>
+      <c r="E43" s="41" t="inlineStr">
+        <is>
+          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="40" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="I43" s="40" t="inlineStr">
         <is>
           <t>越大越危险</t>
         </is>
       </c>
-      <c r="J42" s="40" t="inlineStr">
-        <is>
-          <t>Almqvist 等 1991</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" s="26">
-      <c r="A43" s="44" t="inlineStr">
-        <is>
-          <t>变道/侧刮</t>
-        </is>
-      </c>
-      <c r="B43" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C43" s="39" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="D43" s="40" t="inlineStr">
-        <is>
-          <t>严重度类</t>
-        </is>
-      </c>
-      <c r="E43" s="41" t="inlineStr">
-        <is>
-          <t>ΔV_F = m_L ÷ (m_F + m_L) × |v_F − v_L|（v 为速度向量）</t>
-        </is>
-      </c>
-      <c r="F43" s="40" t="inlineStr">
-        <is>
-          <t>假设撞上后两车粘在一起，各自的速度一下子变多少；轻的一方变化大</t>
-        </is>
-      </c>
-      <c r="G43" s="40" t="inlineStr">
-        <is>
-          <t>车辆质量（按车型或外框大小估）</t>
-        </is>
-      </c>
-      <c r="H43" s="40" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="I43" s="40" t="inlineStr">
-        <is>
-          <t>越大越严重</t>
-        </is>
-      </c>
       <c r="J43" s="40" t="inlineStr">
         <is>
-          <t>事故重建；Shelby 2011；Extended Delta-V 见 Laureshyn 2017</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5971,22 +5800,22 @@
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
-          <t>最近距离 δ</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="D44" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E44" s="41" t="inlineStr">
         <is>
-          <t>δ = 两车外框（矩形）之间的最短距离</t>
+          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
         </is>
       </c>
       <c r="F44" s="40" t="inlineStr">
         <is>
-          <t>不分方向，两车车身最近的地方隔多远</t>
+          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
         </is>
       </c>
       <c r="G44" s="40" t="inlineStr">
@@ -5996,7 +5825,7 @@
       </c>
       <c r="H44" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I44" s="40" t="inlineStr">
@@ -6006,7 +5835,7 @@
       </c>
       <c r="J44" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Venthuruthiyil &amp; Chunchu 2022</t>
         </is>
       </c>
     </row>
@@ -6023,42 +5852,42 @@
       </c>
       <c r="C45" s="39" t="inlineStr">
         <is>
-          <t>接近速度 Δv</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="D45" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E45" s="41" t="inlineStr">
         <is>
-          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+          <t>PET = t_后到者进入冲突区 − t_先到者离开冲突区</t>
         </is>
       </c>
       <c r="F45" s="40" t="inlineStr">
         <is>
-          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+          <t>两个人实际先后经过同一块区域，相差几秒</t>
         </is>
       </c>
       <c r="G45" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>冲突区的定义</t>
         </is>
       </c>
       <c r="H45" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I45" s="40" t="inlineStr">
         <is>
-          <t>越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J45" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Allen 等 1978</t>
         </is>
       </c>
     </row>
@@ -6075,7 +5904,7 @@
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D46" s="40" t="inlineStr">
@@ -6085,17 +5914,17 @@
       </c>
       <c r="E46" s="41" t="inlineStr">
         <is>
-          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
+          <t>GT = t̂_后到者进入冲突区 − t̂_先到者离开冲突区（t̂ 按当前速度和方向预测）</t>
         </is>
       </c>
       <c r="F46" s="40" t="inlineStr">
         <is>
-          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
+          <t>预测的 PET；冲突发生之前就能算</t>
         </is>
       </c>
       <c r="G46" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>冲突区的定义</t>
         </is>
       </c>
       <c r="H46" s="40" t="inlineStr">
@@ -6110,7 +5939,7 @@
       </c>
       <c r="J46" s="40" t="inlineStr">
         <is>
-          <t>Venthuruthiyil &amp; Chunchu 2022</t>
+          <t>Allen 等 1978</t>
         </is>
       </c>
     </row>
@@ -6127,32 +5956,32 @@
       </c>
       <c r="C47" s="39" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="D47" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>距离类</t>
         </is>
       </c>
       <c r="E47" s="41" t="inlineStr">
         <is>
-          <t>PET = t_后到者进入冲突区 − t_先到者离开冲突区</t>
+          <t>PSD = 到冲突点的剩余距离 ÷ [v² ÷ (2·a_max)]</t>
         </is>
       </c>
       <c r="F47" s="40" t="inlineStr">
         <is>
-          <t>两个人实际先后经过同一块区域，相差几秒</t>
+          <t>剩下的距离够不够停车；小于 1 表示刹不住</t>
         </is>
       </c>
       <c r="G47" s="40" t="inlineStr">
         <is>
-          <t>冲突区的定义</t>
+          <t>最大可接受减速度 a_max</t>
         </is>
       </c>
       <c r="H47" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>无单位</t>
         </is>
       </c>
       <c r="I47" s="40" t="inlineStr">
@@ -6179,27 +6008,27 @@
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MPrISM</t>
         </is>
       </c>
       <c r="D48" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>模型预测类</t>
         </is>
       </c>
       <c r="E48" s="41" t="inlineStr">
         <is>
-          <t>GT = t̂_后到者进入冲突区 − t̂_先到者离开冲突区（t̂ 按当前速度和方向预测）</t>
+          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
         </is>
       </c>
       <c r="F48" s="40" t="inlineStr">
         <is>
-          <t>预测的 PET；冲突发生之前就能算</t>
+          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
         </is>
       </c>
       <c r="G48" s="40" t="inlineStr">
         <is>
-          <t>冲突区的定义</t>
+          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
         </is>
       </c>
       <c r="H48" s="40" t="inlineStr">
@@ -6214,7 +6043,7 @@
       </c>
       <c r="J48" s="40" t="inlineStr">
         <is>
-          <t>Allen 等 1978</t>
+          <t>Weng 等 2020</t>
         </is>
       </c>
     </row>
@@ -6226,47 +6055,47 @@
       </c>
       <c r="B49" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C49" s="39" t="inlineStr">
         <is>
-          <t>PSD</t>
+          <t>速度 v</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
         <is>
-          <t>距离类</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E49" s="41" t="inlineStr">
         <is>
-          <t>PSD = 到冲突点的剩余距离 ÷ [v² ÷ (2·a_max)]</t>
+          <t>v = √(v_x² + v_y²)</t>
         </is>
       </c>
       <c r="F49" s="40" t="inlineStr">
         <is>
-          <t>剩下的距离够不够停车；小于 1 表示刹不住</t>
+          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
         </is>
       </c>
       <c r="G49" s="40" t="inlineStr">
         <is>
-          <t>最大可接受减速度 a_max</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="40" t="inlineStr">
         <is>
-          <t>无单位</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="I49" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越大越严重（严重度）</t>
         </is>
       </c>
       <c r="J49" s="40" t="inlineStr">
         <is>
-          <t>Allen 等 1978</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6278,47 +6107,47 @@
       </c>
       <c r="B50" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
-          <t>delta-V</t>
+          <t>纵向加速度 a</t>
         </is>
       </c>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>严重度类</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E50" s="41" t="inlineStr">
         <is>
-          <t>ΔV_F = m_L ÷ (m_F + m_L) × |v_F − v_L|（v 为速度向量）</t>
+          <t>a = dv ÷ dt（负值表示减速）</t>
         </is>
       </c>
       <c r="F50" s="40" t="inlineStr">
         <is>
-          <t>假设撞上后两车粘在一起，各自的速度一下子变多少；轻的一方变化大</t>
+          <t>加速或刹车有多猛；急刹说明有人在避让</t>
         </is>
       </c>
       <c r="G50" s="40" t="inlineStr">
         <is>
-          <t>车辆质量（按车型或外框大小估）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m/s²</t>
         </is>
       </c>
       <c r="I50" s="40" t="inlineStr">
         <is>
-          <t>越大越严重</t>
+          <t>减速越猛越危险</t>
         </is>
       </c>
       <c r="J50" s="40" t="inlineStr">
         <is>
-          <t>事故重建；Shelby 2011；Extended Delta-V 见 Laureshyn 2017</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6330,47 +6159,47 @@
       </c>
       <c r="B51" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C51" s="39" t="inlineStr">
         <is>
-          <t>MPrISM</t>
+          <t>急刹事件</t>
         </is>
       </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>模型预测类</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E51" s="41" t="inlineStr">
         <is>
-          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
+          <t>急刹 = [a(t) &lt; −a_thr]，按次数或持续时间统计</t>
         </is>
       </c>
       <c r="F51" s="40" t="inlineStr">
         <is>
-          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
+          <t>减速超过阈值的时刻；适合用来筛出可疑片段</t>
         </is>
       </c>
       <c r="G51" s="40" t="inlineStr">
         <is>
-          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
+          <t>急刹阈值 a_thr（Google 用 3 m/s²）</t>
         </is>
       </c>
       <c r="H51" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>次 / s</t>
         </is>
       </c>
       <c r="I51" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越多越危险</t>
         </is>
       </c>
       <c r="J51" s="40" t="inlineStr">
         <is>
-          <t>Weng 等 2020</t>
+          <t>Google Research 2026（HBE 定义）</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6216,7 @@
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
-          <t>速度 v</t>
+          <t>横向加速度 a_lat</t>
         </is>
       </c>
       <c r="D52" s="40" t="inlineStr">
@@ -6397,12 +6226,12 @@
       </c>
       <c r="E52" s="41" t="inlineStr">
         <is>
-          <t>v = √(v_x² + v_y²)</t>
+          <t>a_lat = v × ω ≈ v² ÷ R（R 为转弯半径）</t>
         </is>
       </c>
       <c r="F52" s="40" t="inlineStr">
         <is>
-          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
+          <t>转向有多急，例如急打方向、急变道</t>
         </is>
       </c>
       <c r="G52" s="40" t="inlineStr">
@@ -6412,12 +6241,12 @@
       </c>
       <c r="H52" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>m/s²</t>
         </is>
       </c>
       <c r="I52" s="40" t="inlineStr">
         <is>
-          <t>越大越严重（严重度）</t>
+          <t>绝对值越大越危险</t>
         </is>
       </c>
       <c r="J52" s="40" t="inlineStr">
@@ -6439,7 +6268,7 @@
       </c>
       <c r="C53" s="39" t="inlineStr">
         <is>
-          <t>纵向加速度 a</t>
+          <t>加加速度 jerk</t>
         </is>
       </c>
       <c r="D53" s="40" t="inlineStr">
@@ -6449,12 +6278,12 @@
       </c>
       <c r="E53" s="41" t="inlineStr">
         <is>
-          <t>a = dv ÷ dt（负值表示减速）</t>
+          <t>jerk = da ÷ dt</t>
         </is>
       </c>
       <c r="F53" s="40" t="inlineStr">
         <is>
-          <t>加速或刹车有多猛；急刹说明有人在避让</t>
+          <t>加速度变化得有多突然，例如猛踩刹车</t>
         </is>
       </c>
       <c r="G53" s="40" t="inlineStr">
@@ -6464,12 +6293,12 @@
       </c>
       <c r="H53" s="40" t="inlineStr">
         <is>
-          <t>m/s²</t>
+          <t>m/s³</t>
         </is>
       </c>
       <c r="I53" s="40" t="inlineStr">
         <is>
-          <t>减速越猛越危险</t>
+          <t>绝对值越大越危险</t>
         </is>
       </c>
       <c r="J53" s="40" t="inlineStr">
@@ -6491,7 +6320,7 @@
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
-          <t>急刹事件</t>
+          <t>横摆角速度 ω</t>
         </is>
       </c>
       <c r="D54" s="40" t="inlineStr">
@@ -6501,32 +6330,32 @@
       </c>
       <c r="E54" s="41" t="inlineStr">
         <is>
-          <t>急刹 = [a(t) &lt; −a_thr]，按次数或持续时间统计</t>
+          <t>ω = dθ ÷ dt（θ 为车头朝向）</t>
         </is>
       </c>
       <c r="F54" s="40" t="inlineStr">
         <is>
-          <t>减速超过阈值的时刻；适合用来筛出可疑片段</t>
+          <t>车头转得有多快，反映突然打方向</t>
         </is>
       </c>
       <c r="G54" s="40" t="inlineStr">
         <is>
-          <t>急刹阈值 a_thr（Google 用 3 m/s²）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="40" t="inlineStr">
         <is>
-          <t>次 / s</t>
+          <t>rad/s</t>
         </is>
       </c>
       <c r="I54" s="40" t="inlineStr">
         <is>
-          <t>越多越危险</t>
+          <t>绝对值越大越危险</t>
         </is>
       </c>
       <c r="J54" s="40" t="inlineStr">
         <is>
-          <t>Google Research 2026（HBE 定义）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6543,22 +6372,22 @@
       </c>
       <c r="C55" s="39" t="inlineStr">
         <is>
-          <t>横向加速度 a_lat</t>
+          <t>TTC</t>
         </is>
       </c>
       <c r="D55" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E55" s="41" t="inlineStr">
         <is>
-          <t>a_lat = v × ω ≈ v² ÷ R（R 为转弯半径）</t>
+          <t>TTC = d ÷ Δv（Δv &gt; 0；否则记为 ∞）</t>
         </is>
       </c>
       <c r="F55" s="40" t="inlineStr">
         <is>
-          <t>转向有多急，例如急打方向、急变道</t>
+          <t>两车都保持现在的速度，还剩几秒撞上</t>
         </is>
       </c>
       <c r="G55" s="40" t="inlineStr">
@@ -6568,17 +6397,17 @@
       </c>
       <c r="H55" s="40" t="inlineStr">
         <is>
-          <t>m/s²</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I55" s="40" t="inlineStr">
         <is>
-          <t>绝对值越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J55" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hayward 1972</t>
         </is>
       </c>
     </row>
@@ -6595,22 +6424,22 @@
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
-          <t>加加速度 jerk</t>
+          <t>RTTC (ITTC)</t>
         </is>
       </c>
       <c r="D56" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E56" s="41" t="inlineStr">
         <is>
-          <t>jerk = da ÷ dt</t>
+          <t>RTTC = Δv ÷ d = 1 ÷ TTC（不在靠近时为 0）</t>
         </is>
       </c>
       <c r="F56" s="40" t="inlineStr">
         <is>
-          <t>加速度变化得有多突然，例如猛踩刹车</t>
+          <t>TTC 的倒数；不会出现无穷大，排序和求平均方便</t>
         </is>
       </c>
       <c r="G56" s="40" t="inlineStr">
@@ -6620,12 +6449,12 @@
       </c>
       <c r="H56" s="40" t="inlineStr">
         <is>
-          <t>m/s³</t>
+          <t>1/s</t>
         </is>
       </c>
       <c r="I56" s="40" t="inlineStr">
         <is>
-          <t>绝对值越大越危险</t>
+          <t>越大越危险</t>
         </is>
       </c>
       <c r="J56" s="40" t="inlineStr">
@@ -6647,22 +6476,22 @@
       </c>
       <c r="C57" s="39" t="inlineStr">
         <is>
-          <t>横摆角速度 ω</t>
+          <t>2D-TTC</t>
         </is>
       </c>
       <c r="D57" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E57" s="41" t="inlineStr">
         <is>
-          <t>ω = dθ ÷ dt（θ 为车头朝向）</t>
+          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
         </is>
       </c>
       <c r="F57" s="40" t="inlineStr">
         <is>
-          <t>车头转得有多快，反映突然打方向</t>
+          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
         </is>
       </c>
       <c r="G57" s="40" t="inlineStr">
@@ -6672,17 +6501,17 @@
       </c>
       <c r="H57" s="40" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I57" s="40" t="inlineStr">
         <is>
-          <t>绝对值越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J57" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
         </is>
       </c>
     </row>
@@ -6699,27 +6528,27 @@
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
-          <t>TTC</t>
+          <t>TTB</t>
         </is>
       </c>
       <c r="D58" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>时间类·避让时机</t>
         </is>
       </c>
       <c r="E58" s="41" t="inlineStr">
         <is>
-          <t>TTC = d ÷ Δv（Δv &gt; 0；否则记为 ∞）</t>
+          <t>TTB = TTC − Δv ÷ (2·a_max)（前车匀速、后车以最大减速度刹车时的化简式；小于 0 记为 −∞）</t>
         </is>
       </c>
       <c r="F58" s="40" t="inlineStr">
         <is>
-          <t>两车都保持现在的速度，还剩几秒撞上</t>
+          <t>最晚还能等几秒再刹车，并且仍然能避免碰撞</t>
         </is>
       </c>
       <c r="G58" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>最大减速度 a_max</t>
         </is>
       </c>
       <c r="H58" s="40" t="inlineStr">
@@ -6734,7 +6563,7 @@
       </c>
       <c r="J58" s="40" t="inlineStr">
         <is>
-          <t>Hayward 1972</t>
+          <t>TTM 定义（Westhofen 目录）；化简式按定义推导</t>
         </is>
       </c>
     </row>
@@ -6751,198 +6580,198 @@
       </c>
       <c r="C59" s="39" t="inlineStr">
         <is>
-          <t>RTTC (ITTC)</t>
+          <t>DRAC</t>
         </is>
       </c>
       <c r="D59" s="40" t="inlineStr">
         <is>
+          <t>减速度类</t>
+        </is>
+      </c>
+      <c r="E59" s="41" t="inlineStr">
+        <is>
+          <t>DRAC = Δv² ÷ (2·d)（不在靠近时为 0）</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>在间距用完之前把接近速度降到 0，后车至少要多大的减速度</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="40" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="I59" s="40" t="inlineStr">
+        <is>
+          <t>越大越危险</t>
+        </is>
+      </c>
+      <c r="J59" s="40" t="inlineStr">
+        <is>
+          <t>Almqvist 等 1991</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" s="26">
+      <c r="A60" s="46" t="inlineStr">
+        <is>
+          <t>行人/非机动车</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C60" s="39" t="inlineStr">
+        <is>
+          <t>最近距离 δ</t>
+        </is>
+      </c>
+      <c r="D60" s="40" t="inlineStr">
+        <is>
+          <t>原始运动学量</t>
+        </is>
+      </c>
+      <c r="E60" s="41" t="inlineStr">
+        <is>
+          <t>δ = 两车外框（矩形）之间的最短距离</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>不分方向，两车车身最近的地方隔多远</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I60" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J60" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" s="26">
+      <c r="A61" s="46" t="inlineStr">
+        <is>
+          <t>行人/非机动车</t>
+        </is>
+      </c>
+      <c r="B61" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C61" s="39" t="inlineStr">
+        <is>
+          <t>接近速度 Δv</t>
+        </is>
+      </c>
+      <c r="D61" s="40" t="inlineStr">
+        <is>
+          <t>原始运动学量</t>
+        </is>
+      </c>
+      <c r="E61" s="41" t="inlineStr">
+        <is>
+          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+        </is>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+        </is>
+      </c>
+      <c r="G61" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="40" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="I61" s="40" t="inlineStr">
+        <is>
+          <t>越大越危险</t>
+        </is>
+      </c>
+      <c r="J61" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" s="26">
+      <c r="A62" s="46" t="inlineStr">
+        <is>
+          <t>行人/非机动车</t>
+        </is>
+      </c>
+      <c r="B62" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C62" s="39" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="D62" s="40" t="inlineStr">
+        <is>
           <t>时间类·接近程度</t>
         </is>
       </c>
-      <c r="E59" s="41" t="inlineStr">
-        <is>
-          <t>RTTC = Δv ÷ d = 1 ÷ TTC（不在靠近时为 0）</t>
-        </is>
-      </c>
-      <c r="F59" s="40" t="inlineStr">
-        <is>
-          <t>TTC 的倒数；不会出现无穷大，排序和求平均方便</t>
-        </is>
-      </c>
-      <c r="G59" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="40" t="inlineStr">
-        <is>
-          <t>1/s</t>
-        </is>
-      </c>
-      <c r="I59" s="40" t="inlineStr">
-        <is>
-          <t>越大越危险</t>
-        </is>
-      </c>
-      <c r="J59" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" s="26">
-      <c r="A60" s="45" t="inlineStr">
-        <is>
-          <t>交叉/转弯</t>
-        </is>
-      </c>
-      <c r="B60" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C60" s="39" t="inlineStr">
-        <is>
-          <t>2D-TTC</t>
-        </is>
-      </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>时间类·接近程度</t>
-        </is>
-      </c>
-      <c r="E60" s="41" t="inlineStr">
-        <is>
-          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
-        </is>
-      </c>
-      <c r="F60" s="40" t="inlineStr">
-        <is>
-          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
-        </is>
-      </c>
-      <c r="G60" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="40" t="inlineStr">
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>PET = t_后到者进入冲突区 − t_先到者离开冲突区</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>两个人实际先后经过同一块区域，相差几秒</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>冲突区的定义</t>
+        </is>
+      </c>
+      <c r="H62" s="40" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="I60" s="40" t="inlineStr">
+      <c r="I62" s="40" t="inlineStr">
         <is>
           <t>越小越危险</t>
         </is>
       </c>
-      <c r="J60" s="40" t="inlineStr">
-        <is>
-          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" s="26">
-      <c r="A61" s="45" t="inlineStr">
-        <is>
-          <t>交叉/转弯</t>
-        </is>
-      </c>
-      <c r="B61" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C61" s="39" t="inlineStr">
-        <is>
-          <t>TTB</t>
-        </is>
-      </c>
-      <c r="D61" s="40" t="inlineStr">
-        <is>
-          <t>时间类·避让时机</t>
-        </is>
-      </c>
-      <c r="E61" s="41" t="inlineStr">
-        <is>
-          <t>TTB = TTC − Δv ÷ (2·a_max)（前车匀速、后车以最大减速度刹车时的化简式；小于 0 记为 −∞）</t>
-        </is>
-      </c>
-      <c r="F61" s="40" t="inlineStr">
-        <is>
-          <t>最晚还能等几秒再刹车，并且仍然能避免碰撞</t>
-        </is>
-      </c>
-      <c r="G61" s="40" t="inlineStr">
-        <is>
-          <t>最大减速度 a_max</t>
-        </is>
-      </c>
-      <c r="H61" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I61" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J61" s="40" t="inlineStr">
-        <is>
-          <t>TTM 定义（Westhofen 目录）；化简式按定义推导</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" s="26">
-      <c r="A62" s="45" t="inlineStr">
-        <is>
-          <t>交叉/转弯</t>
-        </is>
-      </c>
-      <c r="B62" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>DRAC</t>
-        </is>
-      </c>
-      <c r="D62" s="40" t="inlineStr">
-        <is>
-          <t>减速度类</t>
-        </is>
-      </c>
-      <c r="E62" s="41" t="inlineStr">
-        <is>
-          <t>DRAC = Δv² ÷ (2·d)（不在靠近时为 0）</t>
-        </is>
-      </c>
-      <c r="F62" s="40" t="inlineStr">
-        <is>
-          <t>在间距用完之前把接近速度降到 0，后车至少要多大的减速度</t>
-        </is>
-      </c>
-      <c r="G62" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="40" t="inlineStr">
-        <is>
-          <t>m/s²</t>
-        </is>
-      </c>
-      <c r="I62" s="40" t="inlineStr">
-        <is>
-          <t>越大越危险</t>
-        </is>
-      </c>
       <c r="J62" s="40" t="inlineStr">
         <is>
-          <t>Almqvist 等 1991</t>
+          <t>Allen 等 1978</t>
         </is>
       </c>
     </row>
@@ -6959,32 +6788,32 @@
       </c>
       <c r="C63" s="39" t="inlineStr">
         <is>
-          <t>最近距离 δ</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D63" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E63" s="41" t="inlineStr">
         <is>
-          <t>δ = 两车外框（矩形）之间的最短距离</t>
+          <t>GT = t̂_后到者进入冲突区 − t̂_先到者离开冲突区（t̂ 按当前速度和方向预测）</t>
         </is>
       </c>
       <c r="F63" s="40" t="inlineStr">
         <is>
-          <t>不分方向，两车车身最近的地方隔多远</t>
+          <t>预测的 PET；冲突发生之前就能算</t>
         </is>
       </c>
       <c r="G63" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>冲突区的定义</t>
         </is>
       </c>
       <c r="H63" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I63" s="40" t="inlineStr">
@@ -6994,7 +6823,7 @@
       </c>
       <c r="J63" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Allen 等 1978</t>
         </is>
       </c>
     </row>
@@ -7011,42 +6840,42 @@
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
-          <t>接近速度 Δv</t>
+          <t>MPrISM</t>
         </is>
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>模型预测类</t>
         </is>
       </c>
       <c r="E64" s="41" t="inlineStr">
         <is>
-          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
         </is>
       </c>
       <c r="F64" s="40" t="inlineStr">
         <is>
-          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
         </is>
       </c>
       <c r="G64" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
         </is>
       </c>
       <c r="H64" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I64" s="40" t="inlineStr">
         <is>
-          <t>越大越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J64" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Weng 等 2020</t>
         </is>
       </c>
     </row>
@@ -7058,37 +6887,37 @@
       </c>
       <c r="B65" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C65" s="39" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>横向间距</t>
         </is>
       </c>
       <c r="D65" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E65" s="41" t="inlineStr">
         <is>
-          <t>PET = t_后到者进入冲突区 − t_先到者离开冲突区</t>
+          <t>横向间距 = |横向偏移| − (W_F + W_L) ÷ 2</t>
         </is>
       </c>
       <c r="F65" s="40" t="inlineStr">
         <is>
-          <t>两个人实际先后经过同一块区域，相差几秒</t>
+          <t>并排时两车侧面之间隔多远；负数表示横向已经重叠</t>
         </is>
       </c>
       <c r="G65" s="40" t="inlineStr">
         <is>
-          <t>冲突区的定义</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I65" s="40" t="inlineStr">
@@ -7098,7 +6927,7 @@
       </c>
       <c r="J65" s="40" t="inlineStr">
         <is>
-          <t>Allen 等 1978</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7110,47 +6939,47 @@
       </c>
       <c r="B66" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>速度 v</t>
         </is>
       </c>
       <c r="D66" s="40" t="inlineStr">
         <is>
-          <t>时间类·接近程度</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E66" s="41" t="inlineStr">
         <is>
-          <t>GT = t̂_后到者进入冲突区 − t̂_先到者离开冲突区（t̂ 按当前速度和方向预测）</t>
+          <t>v = √(v_x² + v_y²)</t>
         </is>
       </c>
       <c r="F66" s="40" t="inlineStr">
         <is>
-          <t>预测的 PET；冲突发生之前就能算</t>
+          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
         </is>
       </c>
       <c r="G66" s="40" t="inlineStr">
         <is>
-          <t>冲突区的定义</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="I66" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越大越严重（严重度）</t>
         </is>
       </c>
       <c r="J66" s="40" t="inlineStr">
         <is>
-          <t>Allen 等 1978</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7162,47 +6991,47 @@
       </c>
       <c r="B67" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C67" s="39" t="inlineStr">
         <is>
-          <t>MPrISM</t>
+          <t>纵向加速度 a</t>
         </is>
       </c>
       <c r="D67" s="40" t="inlineStr">
         <is>
-          <t>模型预测类</t>
+          <t>原始运动学量</t>
         </is>
       </c>
       <c r="E67" s="41" t="inlineStr">
         <is>
-          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
+          <t>a = dv ÷ dt（负值表示减速）</t>
         </is>
       </c>
       <c r="F67" s="40" t="inlineStr">
         <is>
-          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
+          <t>加速或刹车有多猛；急刹说明有人在避让</t>
         </is>
       </c>
       <c r="G67" s="40" t="inlineStr">
         <is>
-          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="40" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m/s²</t>
         </is>
       </c>
       <c r="I67" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>减速越猛越危险</t>
         </is>
       </c>
       <c r="J67" s="40" t="inlineStr">
         <is>
-          <t>Weng 等 2020</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7048,7 @@
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
-          <t>横向间距</t>
+          <t>急刹事件</t>
         </is>
       </c>
       <c r="D68" s="40" t="inlineStr">
@@ -7229,32 +7058,32 @@
       </c>
       <c r="E68" s="41" t="inlineStr">
         <is>
-          <t>横向间距 = |横向偏移| − (W_F + W_L) ÷ 2</t>
+          <t>急刹 = [a(t) &lt; −a_thr]，按次数或持续时间统计</t>
         </is>
       </c>
       <c r="F68" s="40" t="inlineStr">
         <is>
-          <t>并排时两车侧面之间隔多远；负数表示横向已经重叠</t>
+          <t>减速超过阈值的时刻；适合用来筛出可疑片段</t>
         </is>
       </c>
       <c r="G68" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>急刹阈值 a_thr（Google 用 3 m/s²）</t>
         </is>
       </c>
       <c r="H68" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>次 / s</t>
         </is>
       </c>
       <c r="I68" s="40" t="inlineStr">
         <is>
-          <t>越小越危险</t>
+          <t>越多越危险</t>
         </is>
       </c>
       <c r="J68" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Google Research 2026（HBE 定义）</t>
         </is>
       </c>
     </row>
@@ -7271,22 +7100,22 @@
       </c>
       <c r="C69" s="39" t="inlineStr">
         <is>
-          <t>速度 v</t>
+          <t>2D-TTC</t>
         </is>
       </c>
       <c r="D69" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E69" s="41" t="inlineStr">
         <is>
-          <t>v = √(v_x² + v_y²)</t>
+          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
         </is>
       </c>
       <c r="F69" s="40" t="inlineStr">
         <is>
-          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
+          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
         </is>
       </c>
       <c r="G69" s="40" t="inlineStr">
@@ -7296,17 +7125,17 @@
       </c>
       <c r="H69" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I69" s="40" t="inlineStr">
         <is>
-          <t>越大越严重（严重度）</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J69" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
         </is>
       </c>
     </row>
@@ -7323,22 +7152,22 @@
       </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
-          <t>纵向加速度 a</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="D70" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E70" s="41" t="inlineStr">
         <is>
-          <t>a = dv ÷ dt（负值表示减速）</t>
+          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
         </is>
       </c>
       <c r="F70" s="40" t="inlineStr">
         <is>
-          <t>加速或刹车有多猛；急刹说明有人在避让</t>
+          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
         </is>
       </c>
       <c r="G70" s="40" t="inlineStr">
@@ -7348,17 +7177,17 @@
       </c>
       <c r="H70" s="40" t="inlineStr">
         <is>
-          <t>m/s²</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I70" s="40" t="inlineStr">
         <is>
-          <t>减速越猛越危险</t>
+          <t>越小越危险</t>
         </is>
       </c>
       <c r="J70" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Venthuruthiyil &amp; Chunchu 2022</t>
         </is>
       </c>
     </row>
@@ -7375,250 +7204,250 @@
       </c>
       <c r="C71" s="39" t="inlineStr">
         <is>
-          <t>急刹事件</t>
+          <t>PSD</t>
         </is>
       </c>
       <c r="D71" s="40" t="inlineStr">
         <is>
+          <t>距离类</t>
+        </is>
+      </c>
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>PSD = 到冲突点的剩余距离 ÷ [v² ÷ (2·a_max)]</t>
+        </is>
+      </c>
+      <c r="F71" s="40" t="inlineStr">
+        <is>
+          <t>剩下的距离够不够停车；小于 1 表示刹不住</t>
+        </is>
+      </c>
+      <c r="G71" s="40" t="inlineStr">
+        <is>
+          <t>最大可接受减速度 a_max</t>
+        </is>
+      </c>
+      <c r="H71" s="40" t="inlineStr">
+        <is>
+          <t>无单位</t>
+        </is>
+      </c>
+      <c r="I71" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J71" s="40" t="inlineStr">
+        <is>
+          <t>Allen 等 1978</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" s="26">
+      <c r="A72" s="47" t="inlineStr">
+        <is>
+          <t>对向/正面</t>
+        </is>
+      </c>
+      <c r="B72" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>最近距离 δ</t>
+        </is>
+      </c>
+      <c r="D72" s="40" t="inlineStr">
+        <is>
           <t>原始运动学量</t>
         </is>
       </c>
-      <c r="E71" s="41" t="inlineStr">
-        <is>
-          <t>急刹 = [a(t) &lt; −a_thr]，按次数或持续时间统计</t>
-        </is>
-      </c>
-      <c r="F71" s="40" t="inlineStr">
-        <is>
-          <t>减速超过阈值的时刻；适合用来筛出可疑片段</t>
-        </is>
-      </c>
-      <c r="G71" s="40" t="inlineStr">
-        <is>
-          <t>急刹阈值 a_thr（Google 用 3 m/s²）</t>
-        </is>
-      </c>
-      <c r="H71" s="40" t="inlineStr">
-        <is>
-          <t>次 / s</t>
-        </is>
-      </c>
-      <c r="I71" s="40" t="inlineStr">
-        <is>
-          <t>越多越危险</t>
-        </is>
-      </c>
-      <c r="J71" s="40" t="inlineStr">
-        <is>
-          <t>Google Research 2026（HBE 定义）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" s="26">
-      <c r="A72" s="46" t="inlineStr">
-        <is>
-          <t>行人/非机动车</t>
-        </is>
-      </c>
-      <c r="B72" s="42" t="inlineStr">
+      <c r="E72" s="41" t="inlineStr">
+        <is>
+          <t>δ = 两车外框（矩形）之间的最短距离</t>
+        </is>
+      </c>
+      <c r="F72" s="40" t="inlineStr">
+        <is>
+          <t>不分方向，两车车身最近的地方隔多远</t>
+        </is>
+      </c>
+      <c r="G72" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I72" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J72" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" s="26">
+      <c r="A73" s="47" t="inlineStr">
+        <is>
+          <t>对向/正面</t>
+        </is>
+      </c>
+      <c r="B73" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C73" s="39" t="inlineStr">
+        <is>
+          <t>接近速度 Δv</t>
+        </is>
+      </c>
+      <c r="D73" s="40" t="inlineStr">
+        <is>
+          <t>原始运动学量</t>
+        </is>
+      </c>
+      <c r="E73" s="41" t="inlineStr">
+        <is>
+          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+        </is>
+      </c>
+      <c r="F73" s="40" t="inlineStr">
+        <is>
+          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+        </is>
+      </c>
+      <c r="G73" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="40" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="I73" s="40" t="inlineStr">
+        <is>
+          <t>越大越危险</t>
+        </is>
+      </c>
+      <c r="J73" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" s="26">
+      <c r="A74" s="47" t="inlineStr">
+        <is>
+          <t>对向/正面</t>
+        </is>
+      </c>
+      <c r="B74" s="42" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="D74" s="40" t="inlineStr">
+        <is>
+          <t>时间类·接近程度</t>
+        </is>
+      </c>
+      <c r="E74" s="41" t="inlineStr">
+        <is>
+          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
+        </is>
+      </c>
+      <c r="F74" s="40" t="inlineStr">
+        <is>
+          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
+        </is>
+      </c>
+      <c r="G74" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="40" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="I74" s="40" t="inlineStr">
+        <is>
+          <t>越小越危险</t>
+        </is>
+      </c>
+      <c r="J74" s="40" t="inlineStr">
+        <is>
+          <t>Venthuruthiyil &amp; Chunchu 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" s="26">
+      <c r="A75" s="47" t="inlineStr">
+        <is>
+          <t>对向/正面</t>
+        </is>
+      </c>
+      <c r="B75" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>2D-TTC</t>
-        </is>
-      </c>
-      <c r="D72" s="40" t="inlineStr">
-        <is>
-          <t>时间类·接近程度</t>
-        </is>
-      </c>
-      <c r="E72" s="41" t="inlineStr">
-        <is>
-          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
-        </is>
-      </c>
-      <c r="F72" s="40" t="inlineStr">
-        <is>
-          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
-        </is>
-      </c>
-      <c r="G72" s="40" t="inlineStr">
+      <c r="C75" s="39" t="inlineStr">
+        <is>
+          <t>间距 d</t>
+        </is>
+      </c>
+      <c r="D75" s="40" t="inlineStr">
+        <is>
+          <t>原始运动学量</t>
+        </is>
+      </c>
+      <c r="E75" s="41" t="inlineStr">
+        <is>
+          <t>d = 前车车尾纵向位置 − 后车车头纵向位置</t>
+        </is>
+      </c>
+      <c r="F75" s="40" t="inlineStr">
+        <is>
+          <t>沿行驶方向两车之间还隔多远；最基础的接近程度指标</t>
+        </is>
+      </c>
+      <c r="G75" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H72" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I72" s="40" t="inlineStr">
+      <c r="H75" s="40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I75" s="40" t="inlineStr">
         <is>
           <t>越小越危险</t>
         </is>
       </c>
-      <c r="J72" s="40" t="inlineStr">
-        <is>
-          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" s="26">
-      <c r="A73" s="46" t="inlineStr">
-        <is>
-          <t>行人/非机动车</t>
-        </is>
-      </c>
-      <c r="B73" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C73" s="39" t="inlineStr">
-        <is>
-          <t>ACT</t>
-        </is>
-      </c>
-      <c r="D73" s="40" t="inlineStr">
-        <is>
-          <t>时间类·接近程度</t>
-        </is>
-      </c>
-      <c r="E73" s="41" t="inlineStr">
-        <is>
-          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
-        </is>
-      </c>
-      <c r="F73" s="40" t="inlineStr">
-        <is>
-          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
-        </is>
-      </c>
-      <c r="G73" s="40" t="inlineStr">
+      <c r="J75" s="40" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I73" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J73" s="40" t="inlineStr">
-        <is>
-          <t>Venthuruthiyil &amp; Chunchu 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" s="26">
-      <c r="A74" s="46" t="inlineStr">
-        <is>
-          <t>行人/非机动车</t>
-        </is>
-      </c>
-      <c r="B74" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>PSD</t>
-        </is>
-      </c>
-      <c r="D74" s="40" t="inlineStr">
-        <is>
-          <t>距离类</t>
-        </is>
-      </c>
-      <c r="E74" s="41" t="inlineStr">
-        <is>
-          <t>PSD = 到冲突点的剩余距离 ÷ [v² ÷ (2·a_max)]</t>
-        </is>
-      </c>
-      <c r="F74" s="40" t="inlineStr">
-        <is>
-          <t>剩下的距离够不够停车；小于 1 表示刹不住</t>
-        </is>
-      </c>
-      <c r="G74" s="40" t="inlineStr">
-        <is>
-          <t>最大可接受减速度 a_max</t>
-        </is>
-      </c>
-      <c r="H74" s="40" t="inlineStr">
-        <is>
-          <t>无单位</t>
-        </is>
-      </c>
-      <c r="I74" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J74" s="40" t="inlineStr">
-        <is>
-          <t>Allen 等 1978</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" s="26">
-      <c r="A75" s="46" t="inlineStr">
-        <is>
-          <t>行人/非机动车</t>
-        </is>
-      </c>
-      <c r="B75" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C75" s="39" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="D75" s="40" t="inlineStr">
-        <is>
-          <t>严重度类</t>
-        </is>
-      </c>
-      <c r="E75" s="41" t="inlineStr">
-        <is>
-          <t>ΔV_F = m_L ÷ (m_F + m_L) × |v_F − v_L|（v 为速度向量）</t>
-        </is>
-      </c>
-      <c r="F75" s="40" t="inlineStr">
-        <is>
-          <t>假设撞上后两车粘在一起，各自的速度一下子变多少；轻的一方变化大</t>
-        </is>
-      </c>
-      <c r="G75" s="40" t="inlineStr">
-        <is>
-          <t>车辆质量（按车型或外框大小估）</t>
-        </is>
-      </c>
-      <c r="H75" s="40" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="I75" s="40" t="inlineStr">
-        <is>
-          <t>越大越严重</t>
-        </is>
-      </c>
-      <c r="J75" s="40" t="inlineStr">
-        <is>
-          <t>事故重建；Shelby 2011；Extended Delta-V 见 Laureshyn 2017</t>
         </is>
       </c>
     </row>
@@ -7630,12 +7459,12 @@
       </c>
       <c r="B76" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C76" s="39" t="inlineStr">
         <is>
-          <t>最近距离 δ</t>
+          <t>横向间距</t>
         </is>
       </c>
       <c r="D76" s="40" t="inlineStr">
@@ -7645,12 +7474,12 @@
       </c>
       <c r="E76" s="41" t="inlineStr">
         <is>
-          <t>δ = 两车外框（矩形）之间的最短距离</t>
+          <t>横向间距 = |横向偏移| − (W_F + W_L) ÷ 2</t>
         </is>
       </c>
       <c r="F76" s="40" t="inlineStr">
         <is>
-          <t>不分方向，两车车身最近的地方隔多远</t>
+          <t>并排时两车侧面之间隔多远；负数表示横向已经重叠</t>
         </is>
       </c>
       <c r="G76" s="40" t="inlineStr">
@@ -7682,12 +7511,12 @@
       </c>
       <c r="B77" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C77" s="39" t="inlineStr">
         <is>
-          <t>接近速度 Δv</t>
+          <t>速度 v</t>
         </is>
       </c>
       <c r="D77" s="40" t="inlineStr">
@@ -7697,12 +7526,12 @@
       </c>
       <c r="E77" s="41" t="inlineStr">
         <is>
-          <t>Δv = v_F − v_L（纵向）；二维时 = 两车最短距离 δ 每秒缩短多少</t>
+          <t>v = √(v_x² + v_y²)</t>
         </is>
       </c>
       <c r="F77" s="40" t="inlineStr">
         <is>
-          <t>两车正以多快的速度靠近；大于 0 表示在靠近</t>
+          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
         </is>
       </c>
       <c r="G77" s="40" t="inlineStr">
@@ -7717,7 +7546,7 @@
       </c>
       <c r="I77" s="40" t="inlineStr">
         <is>
-          <t>越大越危险</t>
+          <t>越大越严重（严重度）</t>
         </is>
       </c>
       <c r="J77" s="40" t="inlineStr">
@@ -7734,12 +7563,12 @@
       </c>
       <c r="B78" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>TTC</t>
         </is>
       </c>
       <c r="D78" s="40" t="inlineStr">
@@ -7749,12 +7578,12 @@
       </c>
       <c r="E78" s="41" t="inlineStr">
         <is>
-          <t>ACT = δ ÷ (δ 每秒缩短多少)；δ = 两车外框最短距离</t>
+          <t>TTC = d ÷ Δv（Δv &gt; 0；否则记为 ∞）</t>
         </is>
       </c>
       <c r="F78" s="40" t="inlineStr">
         <is>
-          <t>二维最短距离除以它的缩短速度；追尾、侧刮、对撞、斜角都能用</t>
+          <t>两车都保持现在的速度，还剩几秒撞上</t>
         </is>
       </c>
       <c r="G78" s="40" t="inlineStr">
@@ -7774,7 +7603,7 @@
       </c>
       <c r="J78" s="40" t="inlineStr">
         <is>
-          <t>Venthuruthiyil &amp; Chunchu 2022</t>
+          <t>Hayward 1972</t>
         </is>
       </c>
     </row>
@@ -7786,47 +7615,47 @@
       </c>
       <c r="B79" s="42" t="inlineStr">
         <is>
-          <t>●</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C79" s="39" t="inlineStr">
         <is>
-          <t>delta-V</t>
+          <t>RTTC (ITTC)</t>
         </is>
       </c>
       <c r="D79" s="40" t="inlineStr">
         <is>
-          <t>严重度类</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E79" s="41" t="inlineStr">
         <is>
-          <t>ΔV_F = m_L ÷ (m_F + m_L) × |v_F − v_L|（v 为速度向量）</t>
+          <t>RTTC = Δv ÷ d = 1 ÷ TTC（不在靠近时为 0）</t>
         </is>
       </c>
       <c r="F79" s="40" t="inlineStr">
         <is>
-          <t>假设撞上后两车粘在一起，各自的速度一下子变多少；轻的一方变化大</t>
+          <t>TTC 的倒数；不会出现无穷大，排序和求平均方便</t>
         </is>
       </c>
       <c r="G79" s="40" t="inlineStr">
         <is>
-          <t>车辆质量（按车型或外框大小估）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H79" s="40" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>1/s</t>
         </is>
       </c>
       <c r="I79" s="40" t="inlineStr">
         <is>
-          <t>越大越严重</t>
+          <t>越大越危险</t>
         </is>
       </c>
       <c r="J79" s="40" t="inlineStr">
         <is>
-          <t>事故重建；Shelby 2011；Extended Delta-V 见 Laureshyn 2017</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7843,22 +7672,22 @@
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
-          <t>间距 d</t>
+          <t>2D-TTC</t>
         </is>
       </c>
       <c r="D80" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>时间类·接近程度</t>
         </is>
       </c>
       <c r="E80" s="41" t="inlineStr">
         <is>
-          <t>d = 前车车尾纵向位置 − 后车车头纵向位置</t>
+          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
         </is>
       </c>
       <c r="F80" s="40" t="inlineStr">
         <is>
-          <t>沿行驶方向两车之间还隔多远；最基础的接近程度指标</t>
+          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
         </is>
       </c>
       <c r="G80" s="40" t="inlineStr">
@@ -7868,7 +7697,7 @@
       </c>
       <c r="H80" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I80" s="40" t="inlineStr">
@@ -7878,7 +7707,7 @@
       </c>
       <c r="J80" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7724,32 @@
       </c>
       <c r="C81" s="39" t="inlineStr">
         <is>
-          <t>横向间距</t>
+          <t>MPrISM</t>
         </is>
       </c>
       <c r="D81" s="40" t="inlineStr">
         <is>
-          <t>原始运动学量</t>
+          <t>模型预测类</t>
         </is>
       </c>
       <c r="E81" s="41" t="inlineStr">
         <is>
-          <t>横向间距 = |横向偏移| − (W_F + W_L) ÷ 2</t>
+          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
         </is>
       </c>
       <c r="F81" s="40" t="inlineStr">
         <is>
-          <t>并排时两车侧面之间隔多远；负数表示横向已经重叠</t>
+          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
         </is>
       </c>
       <c r="G81" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
         </is>
       </c>
       <c r="H81" s="40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I81" s="40" t="inlineStr">
@@ -7930,270 +7759,15 @@
       </c>
       <c r="J81" s="40" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" s="26">
-      <c r="A82" s="47" t="inlineStr">
-        <is>
-          <t>对向/正面</t>
-        </is>
-      </c>
-      <c r="B82" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C82" s="39" t="inlineStr">
-        <is>
-          <t>速度 v</t>
-        </is>
-      </c>
-      <c r="D82" s="40" t="inlineStr">
-        <is>
-          <t>原始运动学量</t>
-        </is>
-      </c>
-      <c r="E82" s="41" t="inlineStr">
-        <is>
-          <t>v = √(v_x² + v_y²)</t>
-        </is>
-      </c>
-      <c r="F82" s="40" t="inlineStr">
-        <is>
-          <t>车开多快；本身不是冲突指标，但决定一旦碰撞有多严重</t>
-        </is>
-      </c>
-      <c r="G82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="40" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="I82" s="40" t="inlineStr">
-        <is>
-          <t>越大越严重（严重度）</t>
-        </is>
-      </c>
-      <c r="J82" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" s="26">
-      <c r="A83" s="47" t="inlineStr">
-        <is>
-          <t>对向/正面</t>
-        </is>
-      </c>
-      <c r="B83" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C83" s="39" t="inlineStr">
-        <is>
-          <t>TTC</t>
-        </is>
-      </c>
-      <c r="D83" s="40" t="inlineStr">
-        <is>
-          <t>时间类·接近程度</t>
-        </is>
-      </c>
-      <c r="E83" s="41" t="inlineStr">
-        <is>
-          <t>TTC = d ÷ Δv（Δv &gt; 0；否则记为 ∞）</t>
-        </is>
-      </c>
-      <c r="F83" s="40" t="inlineStr">
-        <is>
-          <t>两车都保持现在的速度，还剩几秒撞上</t>
-        </is>
-      </c>
-      <c r="G83" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I83" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J83" s="40" t="inlineStr">
-        <is>
-          <t>Hayward 1972</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" s="26">
-      <c r="A84" s="47" t="inlineStr">
-        <is>
-          <t>对向/正面</t>
-        </is>
-      </c>
-      <c r="B84" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C84" s="39" t="inlineStr">
-        <is>
-          <t>RTTC (ITTC)</t>
-        </is>
-      </c>
-      <c r="D84" s="40" t="inlineStr">
-        <is>
-          <t>时间类·接近程度</t>
-        </is>
-      </c>
-      <c r="E84" s="41" t="inlineStr">
-        <is>
-          <t>RTTC = Δv ÷ d = 1 ÷ TTC（不在靠近时为 0）</t>
-        </is>
-      </c>
-      <c r="F84" s="40" t="inlineStr">
-        <is>
-          <t>TTC 的倒数；不会出现无穷大，排序和求平均方便</t>
-        </is>
-      </c>
-      <c r="G84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="40" t="inlineStr">
-        <is>
-          <t>1/s</t>
-        </is>
-      </c>
-      <c r="I84" s="40" t="inlineStr">
-        <is>
-          <t>越大越危险</t>
-        </is>
-      </c>
-      <c r="J84" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" s="26">
-      <c r="A85" s="47" t="inlineStr">
-        <is>
-          <t>对向/正面</t>
-        </is>
-      </c>
-      <c r="B85" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C85" s="39" t="inlineStr">
-        <is>
-          <t>2D-TTC</t>
-        </is>
-      </c>
-      <c r="D85" s="40" t="inlineStr">
-        <is>
-          <t>时间类·接近程度</t>
-        </is>
-      </c>
-      <c r="E85" s="41" t="inlineStr">
-        <is>
-          <t>TTC_纵 = (s_纵 − L_前) ÷ Δv_纵；TTC_横 = (s_横 − W̄) ÷ Δv_横；2D-TTC = min(TTC_纵, TTC_横)（各自要求到那时另一个方向仍然重叠）。几何版：两车外框第一次重叠的时刻</t>
-        </is>
-      </c>
-      <c r="F85" s="40" t="inlineStr">
-        <is>
-          <t>从后面追上还是从侧面刮蹭，取先发生的那个，还剩几秒</t>
-        </is>
-      </c>
-      <c r="G85" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H85" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I85" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J85" s="40" t="inlineStr">
-        <is>
-          <t>Guo、Xie &amp; Keyvan-Ekbatani 2023；演示脚本用的是几何版</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" s="26">
-      <c r="A86" s="47" t="inlineStr">
-        <is>
-          <t>对向/正面</t>
-        </is>
-      </c>
-      <c r="B86" s="42" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>MPrISM</t>
-        </is>
-      </c>
-      <c r="D86" s="40" t="inlineStr">
-        <is>
-          <t>模型预测类</t>
-        </is>
-      </c>
-      <c r="E86" s="41" t="inlineStr">
-        <is>
-          <t>h* = min(对方动作) max(自车动作) 第 n 步两车距离；MPrTTC = 第一个使 h* ≤ C 的时刻</t>
-        </is>
-      </c>
-      <c r="F86" s="40" t="inlineStr">
-        <is>
-          <t>对方尽量往你身上撞、你尽量躲的最坏情况下，几秒后会撞上；预测时长内撞不上算安全</t>
-        </is>
-      </c>
-      <c r="G86" s="40" t="inlineStr">
-        <is>
-          <t>车辆运动模型、动作范围、预测时长、碰撞距离 C（原文：1 s、2 m）</t>
-        </is>
-      </c>
-      <c r="H86" s="40" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="I86" s="40" t="inlineStr">
-        <is>
-          <t>越小越危险</t>
-        </is>
-      </c>
-      <c r="J86" s="40" t="inlineStr">
-        <is>
           <t>Weng 等 2020</t>
         </is>
       </c>
     </row>
+    <row r="82" s="26"/>
+    <row r="83" s="26"/>
+    <row r="84" s="26"/>
+    <row r="85" s="26"/>
+    <row r="86" s="26"/>
     <row r="87" s="26"/>
     <row r="88" s="26"/>
     <row r="89" s="26"/>
@@ -8211,7 +7785,7 @@
     <row r="101" s="26"/>
     <row r="102" s="26"/>
   </sheetData>
-  <autoFilter ref="A5:J86"/>
+  <autoFilter ref="A5:J81"/>
   <mergeCells count="2">
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A2:J2"/>
@@ -8226,7 +7800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="13" customWidth="1" style="26" min="1" max="1"/>
@@ -10322,554 +9896,438 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="23.15" customHeight="1" s="26">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>change in velocity during a (potential) collision</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>严重度</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="P21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="Q21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="R21" s="17" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="S21" s="17" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="T21" s="21" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="U21" s="19" t="inlineStr">
-        <is>
-          <t>◇</t>
-        </is>
-      </c>
-      <c r="V21" s="19" t="inlineStr">
-        <is>
-          <t>◇</t>
-        </is>
-      </c>
-      <c r="W21" s="17" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" s="26"/>
+    <row r="21" s="26"/>
+    <row r="22" s="26">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>✓ 直接算的指标数</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="22">
+        <f>COUNTIF(E6:E20,"✓")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22">
+        <f>COUNTIF(F6:F20,"✓")</f>
+        <v/>
+      </c>
+      <c r="G22" s="22">
+        <f>COUNTIF(G6:G20,"✓")</f>
+        <v/>
+      </c>
+      <c r="H22" s="22">
+        <f>COUNTIF(H6:H20,"✓")</f>
+        <v/>
+      </c>
+      <c r="I22" s="22">
+        <f>COUNTIF(I6:I20,"✓")</f>
+        <v/>
+      </c>
+      <c r="J22" s="22">
+        <f>COUNTIF(J6:J20,"✓")</f>
+        <v/>
+      </c>
+      <c r="K22" s="22">
+        <f>COUNTIF(K6:K20,"✓")</f>
+        <v/>
+      </c>
+      <c r="L22" s="22">
+        <f>COUNTIF(L6:L20,"✓")</f>
+        <v/>
+      </c>
+      <c r="M22" s="22">
+        <f>COUNTIF(M6:M20,"✓")</f>
+        <v/>
+      </c>
+      <c r="N22" s="22">
+        <f>COUNTIF(N6:N20,"✓")</f>
+        <v/>
+      </c>
+      <c r="O22" s="22">
+        <f>COUNTIF(O6:O20,"✓")</f>
+        <v/>
+      </c>
+      <c r="P22" s="22">
+        <f>COUNTIF(P6:P20,"✓")</f>
+        <v/>
+      </c>
+      <c r="Q22" s="22">
+        <f>COUNTIF(Q6:Q20,"✓")</f>
+        <v/>
+      </c>
+      <c r="R22" s="22">
+        <f>COUNTIF(R6:R20,"✓")</f>
+        <v/>
+      </c>
+      <c r="S22" s="22">
+        <f>COUNTIF(S6:S20,"✓")</f>
+        <v/>
+      </c>
+      <c r="T22" s="22">
+        <f>COUNTIF(T6:T20,"✓")</f>
+        <v/>
+      </c>
+      <c r="U22" s="22">
+        <f>COUNTIF(U6:U20,"✓")</f>
+        <v/>
+      </c>
+      <c r="V22" s="22">
+        <f>COUNTIF(V6:V20,"✓")</f>
+        <v/>
+      </c>
+      <c r="W22" s="22">
+        <f>COUNTIF(W6:W20,"✓")</f>
+        <v/>
+      </c>
+    </row>
     <row r="23" s="26">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>✓ 直接算的指标数</t>
+          <t>◐ 数据够、需自设参数的指标数</t>
         </is>
       </c>
       <c r="B23" s="28" t="n"/>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="29" t="n"/>
       <c r="E23" s="22">
-        <f>COUNTIF(E6:E21,"✓")</f>
+        <f>COUNTIF(E6:E20,"◐")</f>
         <v/>
       </c>
       <c r="F23" s="22">
-        <f>COUNTIF(F6:F21,"✓")</f>
+        <f>COUNTIF(F6:F20,"◐")</f>
         <v/>
       </c>
       <c r="G23" s="22">
-        <f>COUNTIF(G6:G21,"✓")</f>
+        <f>COUNTIF(G6:G20,"◐")</f>
         <v/>
       </c>
       <c r="H23" s="22">
-        <f>COUNTIF(H6:H21,"✓")</f>
+        <f>COUNTIF(H6:H20,"◐")</f>
         <v/>
       </c>
       <c r="I23" s="22">
-        <f>COUNTIF(I6:I21,"✓")</f>
+        <f>COUNTIF(I6:I20,"◐")</f>
         <v/>
       </c>
       <c r="J23" s="22">
-        <f>COUNTIF(J6:J21,"✓")</f>
+        <f>COUNTIF(J6:J20,"◐")</f>
         <v/>
       </c>
       <c r="K23" s="22">
-        <f>COUNTIF(K6:K21,"✓")</f>
+        <f>COUNTIF(K6:K20,"◐")</f>
         <v/>
       </c>
       <c r="L23" s="22">
-        <f>COUNTIF(L6:L21,"✓")</f>
+        <f>COUNTIF(L6:L20,"◐")</f>
         <v/>
       </c>
       <c r="M23" s="22">
-        <f>COUNTIF(M6:M21,"✓")</f>
+        <f>COUNTIF(M6:M20,"◐")</f>
         <v/>
       </c>
       <c r="N23" s="22">
-        <f>COUNTIF(N6:N21,"✓")</f>
+        <f>COUNTIF(N6:N20,"◐")</f>
         <v/>
       </c>
       <c r="O23" s="22">
-        <f>COUNTIF(O6:O21,"✓")</f>
+        <f>COUNTIF(O6:O20,"◐")</f>
         <v/>
       </c>
       <c r="P23" s="22">
-        <f>COUNTIF(P6:P21,"✓")</f>
+        <f>COUNTIF(P6:P20,"◐")</f>
         <v/>
       </c>
       <c r="Q23" s="22">
-        <f>COUNTIF(Q6:Q21,"✓")</f>
+        <f>COUNTIF(Q6:Q20,"◐")</f>
         <v/>
       </c>
       <c r="R23" s="22">
-        <f>COUNTIF(R6:R21,"✓")</f>
+        <f>COUNTIF(R6:R20,"◐")</f>
         <v/>
       </c>
       <c r="S23" s="22">
-        <f>COUNTIF(S6:S21,"✓")</f>
+        <f>COUNTIF(S6:S20,"◐")</f>
         <v/>
       </c>
       <c r="T23" s="22">
-        <f>COUNTIF(T6:T21,"✓")</f>
+        <f>COUNTIF(T6:T20,"◐")</f>
         <v/>
       </c>
       <c r="U23" s="22">
-        <f>COUNTIF(U6:U21,"✓")</f>
+        <f>COUNTIF(U6:U20,"◐")</f>
         <v/>
       </c>
       <c r="V23" s="22">
-        <f>COUNTIF(V6:V21,"✓")</f>
+        <f>COUNTIF(V6:V20,"◐")</f>
         <v/>
       </c>
       <c r="W23" s="22">
-        <f>COUNTIF(W6:W21,"✓")</f>
+        <f>COUNTIF(W6:W20,"◐")</f>
         <v/>
       </c>
     </row>
     <row r="24" s="26">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>◐ 数据够、需自设参数的指标数</t>
+          <t>△ 有条件的指标数</t>
         </is>
       </c>
       <c r="B24" s="28" t="n"/>
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="29" t="n"/>
       <c r="E24" s="22">
-        <f>COUNTIF(E6:E21,"◐")</f>
+        <f>COUNTIF(E6:E20,"△")</f>
         <v/>
       </c>
       <c r="F24" s="22">
-        <f>COUNTIF(F6:F21,"◐")</f>
+        <f>COUNTIF(F6:F20,"△")</f>
         <v/>
       </c>
       <c r="G24" s="22">
-        <f>COUNTIF(G6:G21,"◐")</f>
+        <f>COUNTIF(G6:G20,"△")</f>
         <v/>
       </c>
       <c r="H24" s="22">
-        <f>COUNTIF(H6:H21,"◐")</f>
+        <f>COUNTIF(H6:H20,"△")</f>
         <v/>
       </c>
       <c r="I24" s="22">
-        <f>COUNTIF(I6:I21,"◐")</f>
+        <f>COUNTIF(I6:I20,"△")</f>
         <v/>
       </c>
       <c r="J24" s="22">
-        <f>COUNTIF(J6:J21,"◐")</f>
+        <f>COUNTIF(J6:J20,"△")</f>
         <v/>
       </c>
       <c r="K24" s="22">
-        <f>COUNTIF(K6:K21,"◐")</f>
+        <f>COUNTIF(K6:K20,"△")</f>
         <v/>
       </c>
       <c r="L24" s="22">
-        <f>COUNTIF(L6:L21,"◐")</f>
+        <f>COUNTIF(L6:L20,"△")</f>
         <v/>
       </c>
       <c r="M24" s="22">
-        <f>COUNTIF(M6:M21,"◐")</f>
+        <f>COUNTIF(M6:M20,"△")</f>
         <v/>
       </c>
       <c r="N24" s="22">
-        <f>COUNTIF(N6:N21,"◐")</f>
+        <f>COUNTIF(N6:N20,"△")</f>
         <v/>
       </c>
       <c r="O24" s="22">
-        <f>COUNTIF(O6:O21,"◐")</f>
+        <f>COUNTIF(O6:O20,"△")</f>
         <v/>
       </c>
       <c r="P24" s="22">
-        <f>COUNTIF(P6:P21,"◐")</f>
+        <f>COUNTIF(P6:P20,"△")</f>
         <v/>
       </c>
       <c r="Q24" s="22">
-        <f>COUNTIF(Q6:Q21,"◐")</f>
+        <f>COUNTIF(Q6:Q20,"△")</f>
         <v/>
       </c>
       <c r="R24" s="22">
-        <f>COUNTIF(R6:R21,"◐")</f>
+        <f>COUNTIF(R6:R20,"△")</f>
         <v/>
       </c>
       <c r="S24" s="22">
-        <f>COUNTIF(S6:S21,"◐")</f>
+        <f>COUNTIF(S6:S20,"△")</f>
         <v/>
       </c>
       <c r="T24" s="22">
-        <f>COUNTIF(T6:T21,"◐")</f>
+        <f>COUNTIF(T6:T20,"△")</f>
         <v/>
       </c>
       <c r="U24" s="22">
-        <f>COUNTIF(U6:U21,"◐")</f>
+        <f>COUNTIF(U6:U20,"△")</f>
         <v/>
       </c>
       <c r="V24" s="22">
-        <f>COUNTIF(V6:V21,"◐")</f>
+        <f>COUNTIF(V6:V20,"△")</f>
         <v/>
       </c>
       <c r="W24" s="22">
-        <f>COUNTIF(W6:W21,"◐")</f>
+        <f>COUNTIF(W6:W20,"△")</f>
         <v/>
       </c>
     </row>
     <row r="25" s="26">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>△ 有条件的指标数</t>
+          <t>≈ / ◇ 需从画面近似或重建</t>
         </is>
       </c>
       <c r="B25" s="28" t="n"/>
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="29" t="n"/>
       <c r="E25" s="22">
-        <f>COUNTIF(E6:E21,"△")</f>
+        <f>COUNTIF(E6:E20,"≈")+COUNTIF(E6:E20,"◇")</f>
         <v/>
       </c>
       <c r="F25" s="22">
-        <f>COUNTIF(F6:F21,"△")</f>
+        <f>COUNTIF(F6:F20,"≈")+COUNTIF(F6:F20,"◇")</f>
         <v/>
       </c>
       <c r="G25" s="22">
-        <f>COUNTIF(G6:G21,"△")</f>
+        <f>COUNTIF(G6:G20,"≈")+COUNTIF(G6:G20,"◇")</f>
         <v/>
       </c>
       <c r="H25" s="22">
-        <f>COUNTIF(H6:H21,"△")</f>
+        <f>COUNTIF(H6:H20,"≈")+COUNTIF(H6:H20,"◇")</f>
         <v/>
       </c>
       <c r="I25" s="22">
-        <f>COUNTIF(I6:I21,"△")</f>
+        <f>COUNTIF(I6:I20,"≈")+COUNTIF(I6:I20,"◇")</f>
         <v/>
       </c>
       <c r="J25" s="22">
-        <f>COUNTIF(J6:J21,"△")</f>
+        <f>COUNTIF(J6:J20,"≈")+COUNTIF(J6:J20,"◇")</f>
         <v/>
       </c>
       <c r="K25" s="22">
-        <f>COUNTIF(K6:K21,"△")</f>
+        <f>COUNTIF(K6:K20,"≈")+COUNTIF(K6:K20,"◇")</f>
         <v/>
       </c>
       <c r="L25" s="22">
-        <f>COUNTIF(L6:L21,"△")</f>
+        <f>COUNTIF(L6:L20,"≈")+COUNTIF(L6:L20,"◇")</f>
         <v/>
       </c>
       <c r="M25" s="22">
-        <f>COUNTIF(M6:M21,"△")</f>
+        <f>COUNTIF(M6:M20,"≈")+COUNTIF(M6:M20,"◇")</f>
         <v/>
       </c>
       <c r="N25" s="22">
-        <f>COUNTIF(N6:N21,"△")</f>
+        <f>COUNTIF(N6:N20,"≈")+COUNTIF(N6:N20,"◇")</f>
         <v/>
       </c>
       <c r="O25" s="22">
-        <f>COUNTIF(O6:O21,"△")</f>
+        <f>COUNTIF(O6:O20,"≈")+COUNTIF(O6:O20,"◇")</f>
         <v/>
       </c>
       <c r="P25" s="22">
-        <f>COUNTIF(P6:P21,"△")</f>
+        <f>COUNTIF(P6:P20,"≈")+COUNTIF(P6:P20,"◇")</f>
         <v/>
       </c>
       <c r="Q25" s="22">
-        <f>COUNTIF(Q6:Q21,"△")</f>
+        <f>COUNTIF(Q6:Q20,"≈")+COUNTIF(Q6:Q20,"◇")</f>
         <v/>
       </c>
       <c r="R25" s="22">
-        <f>COUNTIF(R6:R21,"△")</f>
+        <f>COUNTIF(R6:R20,"≈")+COUNTIF(R6:R20,"◇")</f>
         <v/>
       </c>
       <c r="S25" s="22">
-        <f>COUNTIF(S6:S21,"△")</f>
+        <f>COUNTIF(S6:S20,"≈")+COUNTIF(S6:S20,"◇")</f>
         <v/>
       </c>
       <c r="T25" s="22">
-        <f>COUNTIF(T6:T21,"△")</f>
+        <f>COUNTIF(T6:T20,"≈")+COUNTIF(T6:T20,"◇")</f>
         <v/>
       </c>
       <c r="U25" s="22">
-        <f>COUNTIF(U6:U21,"△")</f>
+        <f>COUNTIF(U6:U20,"≈")+COUNTIF(U6:U20,"◇")</f>
         <v/>
       </c>
       <c r="V25" s="22">
-        <f>COUNTIF(V6:V21,"△")</f>
+        <f>COUNTIF(V6:V20,"≈")+COUNTIF(V6:V20,"◇")</f>
         <v/>
       </c>
       <c r="W25" s="22">
-        <f>COUNTIF(W6:W21,"△")</f>
+        <f>COUNTIF(W6:W20,"≈")+COUNTIF(W6:W20,"◇")</f>
         <v/>
       </c>
     </row>
     <row r="26" s="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>≈ / ◇ 需从画面近似或重建</t>
+          <t>✗ 算不了的指标数</t>
         </is>
       </c>
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="29" t="n"/>
       <c r="E26" s="22">
-        <f>COUNTIF(E6:E21,"≈")+COUNTIF(E6:E21,"◇")</f>
+        <f>COUNTIF(E6:E20,"✗")</f>
         <v/>
       </c>
       <c r="F26" s="22">
-        <f>COUNTIF(F6:F21,"≈")+COUNTIF(F6:F21,"◇")</f>
+        <f>COUNTIF(F6:F20,"✗")</f>
         <v/>
       </c>
       <c r="G26" s="22">
-        <f>COUNTIF(G6:G21,"≈")+COUNTIF(G6:G21,"◇")</f>
+        <f>COUNTIF(G6:G20,"✗")</f>
         <v/>
       </c>
       <c r="H26" s="22">
-        <f>COUNTIF(H6:H21,"≈")+COUNTIF(H6:H21,"◇")</f>
+        <f>COUNTIF(H6:H20,"✗")</f>
         <v/>
       </c>
       <c r="I26" s="22">
-        <f>COUNTIF(I6:I21,"≈")+COUNTIF(I6:I21,"◇")</f>
+        <f>COUNTIF(I6:I20,"✗")</f>
         <v/>
       </c>
       <c r="J26" s="22">
-        <f>COUNTIF(J6:J21,"≈")+COUNTIF(J6:J21,"◇")</f>
+        <f>COUNTIF(J6:J20,"✗")</f>
         <v/>
       </c>
       <c r="K26" s="22">
-        <f>COUNTIF(K6:K21,"≈")+COUNTIF(K6:K21,"◇")</f>
+        <f>COUNTIF(K6:K20,"✗")</f>
         <v/>
       </c>
       <c r="L26" s="22">
-        <f>COUNTIF(L6:L21,"≈")+COUNTIF(L6:L21,"◇")</f>
+        <f>COUNTIF(L6:L20,"✗")</f>
         <v/>
       </c>
       <c r="M26" s="22">
-        <f>COUNTIF(M6:M21,"≈")+COUNTIF(M6:M21,"◇")</f>
+        <f>COUNTIF(M6:M20,"✗")</f>
         <v/>
       </c>
       <c r="N26" s="22">
-        <f>COUNTIF(N6:N21,"≈")+COUNTIF(N6:N21,"◇")</f>
+        <f>COUNTIF(N6:N20,"✗")</f>
         <v/>
       </c>
       <c r="O26" s="22">
-        <f>COUNTIF(O6:O21,"≈")+COUNTIF(O6:O21,"◇")</f>
+        <f>COUNTIF(O6:O20,"✗")</f>
         <v/>
       </c>
       <c r="P26" s="22">
-        <f>COUNTIF(P6:P21,"≈")+COUNTIF(P6:P21,"◇")</f>
+        <f>COUNTIF(P6:P20,"✗")</f>
         <v/>
       </c>
       <c r="Q26" s="22">
-        <f>COUNTIF(Q6:Q21,"≈")+COUNTIF(Q6:Q21,"◇")</f>
+        <f>COUNTIF(Q6:Q20,"✗")</f>
         <v/>
       </c>
       <c r="R26" s="22">
-        <f>COUNTIF(R6:R21,"≈")+COUNTIF(R6:R21,"◇")</f>
+        <f>COUNTIF(R6:R20,"✗")</f>
         <v/>
       </c>
       <c r="S26" s="22">
-        <f>COUNTIF(S6:S21,"≈")+COUNTIF(S6:S21,"◇")</f>
+        <f>COUNTIF(S6:S20,"✗")</f>
         <v/>
       </c>
       <c r="T26" s="22">
-        <f>COUNTIF(T6:T21,"≈")+COUNTIF(T6:T21,"◇")</f>
+        <f>COUNTIF(T6:T20,"✗")</f>
         <v/>
       </c>
       <c r="U26" s="22">
-        <f>COUNTIF(U6:U21,"≈")+COUNTIF(U6:U21,"◇")</f>
+        <f>COUNTIF(U6:U20,"✗")</f>
         <v/>
       </c>
       <c r="V26" s="22">
-        <f>COUNTIF(V6:V21,"≈")+COUNTIF(V6:V21,"◇")</f>
+        <f>COUNTIF(V6:V20,"✗")</f>
         <v/>
       </c>
       <c r="W26" s="22">
-        <f>COUNTIF(W6:W21,"≈")+COUNTIF(W6:W21,"◇")</f>
+        <f>COUNTIF(W6:W20,"✗")</f>
         <v/>
       </c>
     </row>
-    <row r="27" s="26">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>✗ 算不了的指标数</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="n"/>
-      <c r="C27" s="28" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="22">
-        <f>COUNTIF(E6:E21,"✗")</f>
-        <v/>
-      </c>
-      <c r="F27" s="22">
-        <f>COUNTIF(F6:F21,"✗")</f>
-        <v/>
-      </c>
-      <c r="G27" s="22">
-        <f>COUNTIF(G6:G21,"✗")</f>
-        <v/>
-      </c>
-      <c r="H27" s="22">
-        <f>COUNTIF(H6:H21,"✗")</f>
-        <v/>
-      </c>
-      <c r="I27" s="22">
-        <f>COUNTIF(I6:I21,"✗")</f>
-        <v/>
-      </c>
-      <c r="J27" s="22">
-        <f>COUNTIF(J6:J21,"✗")</f>
-        <v/>
-      </c>
-      <c r="K27" s="22">
-        <f>COUNTIF(K6:K21,"✗")</f>
-        <v/>
-      </c>
-      <c r="L27" s="22">
-        <f>COUNTIF(L6:L21,"✗")</f>
-        <v/>
-      </c>
-      <c r="M27" s="22">
-        <f>COUNTIF(M6:M21,"✗")</f>
-        <v/>
-      </c>
-      <c r="N27" s="22">
-        <f>COUNTIF(N6:N21,"✗")</f>
-        <v/>
-      </c>
-      <c r="O27" s="22">
-        <f>COUNTIF(O6:O21,"✗")</f>
-        <v/>
-      </c>
-      <c r="P27" s="22">
-        <f>COUNTIF(P6:P21,"✗")</f>
-        <v/>
-      </c>
-      <c r="Q27" s="22">
-        <f>COUNTIF(Q6:Q21,"✗")</f>
-        <v/>
-      </c>
-      <c r="R27" s="22">
-        <f>COUNTIF(R6:R21,"✗")</f>
-        <v/>
-      </c>
-      <c r="S27" s="22">
-        <f>COUNTIF(S6:S21,"✗")</f>
-        <v/>
-      </c>
-      <c r="T27" s="22">
-        <f>COUNTIF(T6:T21,"✗")</f>
-        <v/>
-      </c>
-      <c r="U27" s="22">
-        <f>COUNTIF(U6:U21,"✗")</f>
-        <v/>
-      </c>
-      <c r="V27" s="22">
-        <f>COUNTIF(V6:V21,"✗")</f>
-        <v/>
-      </c>
-      <c r="W27" s="22">
-        <f>COUNTIF(W6:W21,"✗")</f>
-        <v/>
-      </c>
-    </row>
+    <row r="27" s="26"/>
     <row r="28" s="26"/>
     <row r="29" s="26"/>
     <row r="30" s="26"/>
@@ -10881,13 +10339,13 @@
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="T2:W2"/>
     <mergeCell ref="M2:S2"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="E2:L2"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A24:D24"/>
   </mergeCells>
@@ -11093,7 +10551,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>delta-V</t>
+          <t>（原来受影响的 delta-V 已删除，这一条目前不影响任何指标）</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -11326,11 +10784,11 @@
         </is>
       </c>
       <c r="J3" s="23">
-        <f>COUNTIF(指标×数据集!R6:R21,"✓")</f>
+        <f>COUNTIF(指标×数据集!R6:R20,"✓")</f>
         <v/>
       </c>
       <c r="K3" s="23">
-        <f>COUNTIF(指标×数据集!R6:R21,"◐")</f>
+        <f>COUNTIF(指标×数据集!R6:R20,"◐")</f>
         <v/>
       </c>
       <c r="L3" s="15" t="inlineStr">
@@ -11391,11 +10849,11 @@
         </is>
       </c>
       <c r="J4" s="23">
-        <f>COUNTIF(指标×数据集!N6:N21,"✓")</f>
+        <f>COUNTIF(指标×数据集!N6:N20,"✓")</f>
         <v/>
       </c>
       <c r="K4" s="23">
-        <f>COUNTIF(指标×数据集!N6:N21,"◐")</f>
+        <f>COUNTIF(指标×数据集!N6:N20,"◐")</f>
         <v/>
       </c>
       <c r="L4" s="15" t="inlineStr">
@@ -11456,11 +10914,11 @@
         </is>
       </c>
       <c r="J5" s="23">
-        <f>COUNTIF(指标×数据集!O6:O21,"✓")</f>
+        <f>COUNTIF(指标×数据集!O6:O20,"✓")</f>
         <v/>
       </c>
       <c r="K5" s="23">
-        <f>COUNTIF(指标×数据集!O6:O21,"◐")</f>
+        <f>COUNTIF(指标×数据集!O6:O20,"◐")</f>
         <v/>
       </c>
       <c r="L5" s="15" t="inlineStr">
@@ -11521,11 +10979,11 @@
         </is>
       </c>
       <c r="J6" s="23">
-        <f>COUNTIF(指标×数据集!M6:M21,"✓")</f>
+        <f>COUNTIF(指标×数据集!M6:M20,"✓")</f>
         <v/>
       </c>
       <c r="K6" s="23">
-        <f>COUNTIF(指标×数据集!M6:M21,"◐")</f>
+        <f>COUNTIF(指标×数据集!M6:M20,"◐")</f>
         <v/>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -11586,11 +11044,11 @@
         </is>
       </c>
       <c r="J7" s="23">
-        <f>COUNTIF(指标×数据集!P6:P21,"✓")</f>
+        <f>COUNTIF(指标×数据集!P6:P20,"✓")</f>
         <v/>
       </c>
       <c r="K7" s="23">
-        <f>COUNTIF(指标×数据集!P6:P21,"◐")</f>
+        <f>COUNTIF(指标×数据集!P6:P20,"◐")</f>
         <v/>
       </c>
       <c r="L7" s="15" t="inlineStr">
@@ -11651,11 +11109,11 @@
         </is>
       </c>
       <c r="J8" s="23">
-        <f>COUNTIF(指标×数据集!Q6:Q21,"✓")</f>
+        <f>COUNTIF(指标×数据集!Q6:Q20,"✓")</f>
         <v/>
       </c>
       <c r="K8" s="23">
-        <f>COUNTIF(指标×数据集!Q6:Q21,"◐")</f>
+        <f>COUNTIF(指标×数据集!Q6:Q20,"◐")</f>
         <v/>
       </c>
       <c r="L8" s="15" t="inlineStr">
@@ -11716,11 +11174,11 @@
         </is>
       </c>
       <c r="J9" s="23">
-        <f>COUNTIF(指标×数据集!U6:U21,"✓")</f>
+        <f>COUNTIF(指标×数据集!U6:U20,"✓")</f>
         <v/>
       </c>
       <c r="K9" s="23">
-        <f>COUNTIF(指标×数据集!U6:U21,"◐")</f>
+        <f>COUNTIF(指标×数据集!U6:U20,"◐")</f>
         <v/>
       </c>
       <c r="L9" s="15" t="inlineStr">
@@ -11781,11 +11239,11 @@
         </is>
       </c>
       <c r="J10" s="23">
-        <f>COUNTIF(指标×数据集!T6:T21,"✓")</f>
+        <f>COUNTIF(指标×数据集!T6:T20,"✓")</f>
         <v/>
       </c>
       <c r="K10" s="23">
-        <f>COUNTIF(指标×数据集!T6:T21,"◐")</f>
+        <f>COUNTIF(指标×数据集!T6:T20,"◐")</f>
         <v/>
       </c>
       <c r="L10" s="15" t="inlineStr">
@@ -11846,11 +11304,11 @@
         </is>
       </c>
       <c r="J11" s="23">
-        <f>COUNTIF(指标×数据集!V6:V21,"✓")</f>
+        <f>COUNTIF(指标×数据集!V6:V20,"✓")</f>
         <v/>
       </c>
       <c r="K11" s="23">
-        <f>COUNTIF(指标×数据集!V6:V21,"◐")</f>
+        <f>COUNTIF(指标×数据集!V6:V20,"◐")</f>
         <v/>
       </c>
       <c r="L11" s="15" t="inlineStr">
@@ -11875,7 +11333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="22" customWidth="1" style="26" min="1" max="1"/>
@@ -16428,519 +15886,25 @@
         </is>
       </c>
     </row>
-    <row r="170" s="26">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>CitySim</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="D170" s="24" t="inlineStr">
-        <is>
-          <t>C6 自设参数</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>[C6] 车型/质量：没有车型字段，要按外框尺寸估车型和质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" s="26">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>NGSIM</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D171" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" s="26">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>highD</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D172" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" s="26">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>exiD</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D173" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" s="26">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>inD / rounD</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D174" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" s="26">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>SinD</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D175" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" s="26">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>INTERACTION</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="D176" s="24" t="inlineStr">
-        <is>
-          <t>C6 自设参数</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>[C6] 车型/质量：只区分机动车与行人/自行车，不区分货车；[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" s="26">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>TGSIM</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D177" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" s="26">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>nuScenes</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D178" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" s="26">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Argoverse 2 传感器</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D179" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" s="26">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Waymo 感知</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="D180" s="24" t="inlineStr">
-        <is>
-          <t>C6 自设参数</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>[C6] 车型/质量：只有车辆、行人、骑车人、标志四类，不区分货车，要按外框尺寸估质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" s="26">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>KITTI 跟踪</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D181" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="24.9" customHeight="1" s="26">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>PandaSet</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D182" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" s="26">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>nuPlan</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="D183" s="24" t="inlineStr">
-        <is>
-          <t>C6 自设参数</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>[C6] 车型/质量：物体类别只有"车辆"，不区分轿车和货车，要按外框尺寸估质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" s="26">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>Waymo 运动预测</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="D184" s="24" t="inlineStr">
-        <is>
-          <t>C6 自设参数</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>[C6] 车型/质量：只分车辆、行人、骑车人，不区分货车；[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="24.9" customHeight="1" s="26">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>DeepAccident（仿真）</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>◐</t>
-        </is>
-      </c>
-      <c r="D185" s="24" t="inlineStr">
-        <is>
-          <t>自设参数</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" s="26">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>Waymo WOD-E2E</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C186" s="7" t="inlineStr">
-        <is>
-          <t>◇</t>
-        </is>
-      </c>
-      <c r="D186" s="24" t="inlineStr">
-        <is>
-          <t>需 CV 重建</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>数据里没有周围物体的 3D 轨迹，需先用 CV（3D 检测/单目深度）从画面重建，误差大</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" s="26">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Nexar / DoTA / CCD</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C187" s="7" t="inlineStr">
-        <is>
-          <t>◇</t>
-        </is>
-      </c>
-      <c r="D187" s="24" t="inlineStr">
-        <is>
-          <t>需 CV 重建</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>数据里没有周围物体的 3D 轨迹，需先用 CV（3D 检测/单目深度）从画面重建，误差大</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" s="26">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>100-Car 公开部分</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="C188" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="D188" s="24" t="inlineStr">
-        <is>
-          <t>C6 自设参数</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>[C6] 车型/质量：前车车型未知，按小汽车估质量；[P] 需自设：车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-    </row>
+    <row r="170" s="26"/>
+    <row r="171" s="26"/>
+    <row r="172" s="26"/>
+    <row r="173" s="26"/>
+    <row r="174" s="26"/>
+    <row r="175" s="26"/>
+    <row r="176" s="26"/>
+    <row r="177" s="26"/>
+    <row r="178" s="26"/>
+    <row r="179" s="26"/>
+    <row r="180" s="26"/>
+    <row r="181" s="26"/>
+    <row r="182" ht="24.9" customHeight="1" s="26"/>
+    <row r="183" s="26"/>
+    <row r="184" s="26"/>
+    <row r="185" ht="24.9" customHeight="1" s="26"/>
+    <row r="186" s="26"/>
+    <row r="187" s="26"/>
+    <row r="188" s="26"/>
     <row r="189" s="26"/>
     <row r="190" s="26"/>
     <row r="191" s="26"/>
@@ -17075,7 +16039,7 @@
     <row r="320" s="26"/>
     <row r="321" s="26"/>
   </sheetData>
-  <autoFilter ref="A2:E188"/>
+  <autoFilter ref="A2:E169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18128,7 +17092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="13" customWidth="1" style="26" min="1" max="1"/>
@@ -18138,8 +17102,8 @@
     <col width="8" customWidth="1" style="26" min="5" max="5"/>
     <col width="10" customWidth="1" style="26" min="6" max="7"/>
     <col width="9" customWidth="1" style="26" min="8" max="9"/>
-    <col width="22" customWidth="1" style="26" min="10" max="10"/>
-    <col width="48" customWidth="1" style="26" min="11" max="11"/>
+    <col width="22" customWidth="1" style="26" min="9" max="9"/>
+    <col width="48" customWidth="1" style="26" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.9" customHeight="1" s="26">
@@ -18185,15 +17149,10 @@
       </c>
       <c r="I1" s="12" t="inlineStr">
         <is>
-          <t>车型/质量</t>
+          <t>需自设什么</t>
         </is>
       </c>
       <c r="J1" s="12" t="inlineStr">
-        <is>
-          <t>需自设什么</t>
-        </is>
-      </c>
-      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -18228,9 +17187,8 @@
       </c>
       <c r="G2" s="24" t="n"/>
       <c r="H2" s="24" t="n"/>
-      <c r="I2" s="24" t="n"/>
+      <c r="I2" s="15" t="n"/>
       <c r="J2" s="15" t="n"/>
-      <c r="K2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -18261,9 +17219,8 @@
           <t>●</t>
         </is>
       </c>
-      <c r="I3" s="24" t="n"/>
-      <c r="J3" s="15" t="n"/>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>有外框时用车身边缘计算更准</t>
         </is>
@@ -18298,9 +17255,8 @@
       </c>
       <c r="G4" s="24" t="n"/>
       <c r="H4" s="24" t="n"/>
-      <c r="I4" s="24" t="n"/>
+      <c r="I4" s="15" t="n"/>
       <c r="J4" s="15" t="n"/>
-      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -18335,9 +17291,8 @@
       </c>
       <c r="G5" s="24" t="n"/>
       <c r="H5" s="24" t="n"/>
-      <c r="I5" s="24" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>需要两车加速度</t>
         </is>
@@ -18372,9 +17327,8 @@
       </c>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
+      <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
-      <c r="K6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -18405,9 +17359,8 @@
         </is>
       </c>
       <c r="H7" s="24" t="n"/>
-      <c r="I7" s="24" t="n"/>
+      <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
-      <c r="K7" s="15" t="n"/>
     </row>
     <row r="8" ht="23.15" customHeight="1" s="26">
       <c r="A8" s="14" t="inlineStr">
@@ -18438,13 +17391,12 @@
         </is>
       </c>
       <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>车辆动力学模型和最坏情况的设定</t>
+        </is>
+      </c>
       <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>车辆动力学模型和最坏情况的设定</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>需车辆动力学模型和最坏情况设定</t>
         </is>
@@ -18479,9 +17431,8 @@
       </c>
       <c r="G9" s="24" t="n"/>
       <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
+      <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
-      <c r="K9" s="15" t="n"/>
     </row>
     <row r="10" s="26">
       <c r="A10" s="14" t="inlineStr">
@@ -18512,13 +17463,12 @@
       </c>
       <c r="G10" s="24" t="n"/>
       <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>最大可接受减速度</t>
+        </is>
+      </c>
       <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>最大可接受减速度</t>
-        </is>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>需最大可接受减速度</t>
         </is>
@@ -18553,13 +17503,12 @@
       </c>
       <c r="G11" s="24" t="n"/>
       <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>反应时间、急刹减速度</t>
+        </is>
+      </c>
       <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>反应时间、急刹减速度</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>需反应时间和急刹减速度</t>
         </is>
@@ -18594,13 +17543,12 @@
       </c>
       <c r="G12" s="24" t="n"/>
       <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>安全时距（NHTSA 那篇用 1.4 秒）</t>
+        </is>
+      </c>
       <c r="J12" s="15" t="inlineStr">
-        <is>
-          <t>安全时距（NHTSA 那篇用 1.4 秒）</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>需设定安全时距（NHTSA 那篇用 1.4 秒）</t>
         </is>
@@ -18635,13 +17583,12 @@
       </c>
       <c r="G13" s="24" t="n"/>
       <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>最大减速度</t>
+        </is>
+      </c>
       <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>最大减速度</t>
-        </is>
-      </c>
-      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>需最大减速度</t>
         </is>
@@ -18680,9 +17627,8 @@
       </c>
       <c r="G14" s="24" t="n"/>
       <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>基于 MTTC，需要加速度</t>
         </is>
@@ -18717,9 +17663,8 @@
           <t>●</t>
         </is>
       </c>
-      <c r="I15" s="24" t="n"/>
+      <c r="I15" s="15" t="n"/>
       <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
     </row>
     <row r="16" s="26">
       <c r="A16" s="14" t="inlineStr">
@@ -18750,59 +17695,18 @@
         </is>
       </c>
       <c r="H16" s="24" t="n"/>
-      <c r="I16" s="24" t="n"/>
+      <c r="I16" s="15" t="n"/>
       <c r="J16" s="15" t="n"/>
-      <c r="K16" s="15" t="n"/>
-    </row>
-    <row r="17" s="26">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>delta-V</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>change in velocity during a (potential) collision</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>严重度</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="24" t="n"/>
-      <c r="H17" s="24" t="n"/>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr">
-        <is>
-          <t>车辆质量（按车型取典型值）</t>
-        </is>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>按车型取典型质量</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" s="26"/>
-    <row r="19" ht="24.9" customHeight="1" s="26">
-      <c r="A19" s="33" t="inlineStr">
+    </row>
+    <row r="17" s="26"/>
+    <row r="18" ht="24.9" customHeight="1" s="26">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>● 必需</t>
         </is>
       </c>
     </row>
+    <row r="19" ht="24.9" customHeight="1" s="26"/>
     <row r="20" ht="24.9" customHeight="1" s="26"/>
     <row r="21" ht="24.9" customHeight="1" s="26"/>
     <row r="22" ht="24.9" customHeight="1" s="26"/>
